--- a/PTBR/Lang/PTBR/Dialog/dialog.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/dialog.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId1"/>
@@ -373,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.11" customWidth="1" style="13" min="1" max="1"/>
@@ -413,9 +413,9 @@
           <t>food1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Temos alguns pratos especiais quentinhos esperando por você. #1 Orens e são todos seus.</t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Temos pratos especiais quentinhos esperando por você. #1 orens e são todos seus.</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -435,9 +435,9 @@
           <t>food2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aqui, aproveite sua refeição!</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Aqui, bom apetite!</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -457,9 +457,9 @@
           <t>healer1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Está sofrendo com alguma ferida ou enfermidade? #1 Orens e iniciarei seu tratamento imediatamente.</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Está sofrendo com algum ferimento ou doença? #1 orens e começo seu tratamento imediatamente.</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -479,9 +479,9 @@
           <t>healer2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Então fique parado. Seu corpo estará curado em instantes.</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Então fique parado. Deixo seu corpo são em um instante.</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -501,9 +501,9 @@
           <t>appraise1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Você tem algum item não identificado em sua mochila? Por #1 Orens, farei a avaliação de todos para você.</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Tem itens não identificados na mochila? Por #1 orens, avalio todos para você.</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -523,9 +523,9 @@
           <t>appraise2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Começarei a avaliar seus itens agora mesmo. Espere aqui um pouco.</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Começo a avaliar seus itens agora mesmo. Espere aqui um pouco.</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -545,9 +545,9 @@
           <t>appraise3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Parece que você não tem nada para ser avaliado.</t>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Parece que você não tem nada para avaliar.</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -567,9 +567,9 @@
           <t>expand1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>São necessárias #2 barras de ouro para expandir sua casa.</t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>#2 barras de ouro são necessárias para expandir seu lar.</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -589,9 +589,9 @@
           <t>expand2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Pronto, sua casa foi expandida!</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Pronto, seu lar foi expandido!</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -611,9 +611,9 @@
           <t>expand3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Parece que sua casa não pode ser expandida.</t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Parece que seu lar não pode ser expandido.</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -635,8 +635,8 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>_x000D_
-Atualmente, seu pagamento adicional de impostos mensais para Mysilia é de #1. Se quiser mudar o valor, é só me avisar.</t>
+          <t xml:space="preserve">
+Atualmente, seu pagamento mensal adicional de imposto a Mysilia é #1. Se quiser mudar o valor, é só avisar.</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -657,9 +657,9 @@
           <t>extraTax2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Certo, alterei seu pagamento adicional de impostos para Mysilia para #1.</t>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Pronto, mudei seu pagamento adicional de imposto a Mysilia para #1.</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -679,9 +679,9 @@
           <t>banker1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Você tem atualmente #1 Orens em sua conta. Quanto deseja depositar?</t>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Você tem #1 orens na conta. Quanto quer depositar?</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -701,9 +701,9 @@
           <t>banker2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Você tem atualmente #1 Orens em sua conta. Quanto deseja sacar?</t>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Você tem #1 orens na conta. Quanto quer sacar?</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -723,7 +723,7 @@
           <t>banker3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Muito bem. O dinheiro será adicionado à sua conta.</t>
         </is>
@@ -745,9 +745,9 @@
           <t>banker4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Muito bem. Aqui está o seu dinheiro.</t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Muito bem. Aqui está seu dinheiro.</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -767,9 +767,9 @@
           <t>noDrawingRoom</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Você não tem uma sala de recepção para visitantes.</t>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Você não tem uma sala de visitas para hóspedes.</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -789,7 +789,7 @@
           <t>nomoney</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Aparentemente, você não tem dinheiro suficiente.</t>
         </is>
@@ -811,9 +811,9 @@
           <t>alreadyFull</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Parece que você já está satisfeito.</t>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Parece que você já está cheio.</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -833,9 +833,9 @@
           <t>questAccept</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Vai aceitar meu pedido? Muito bem, estou contando com você.</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Vai aceitar meu pedido? Muito bem, conto com você.</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -855,9 +855,9 @@
           <t>questFull</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Parece que você está com muitos pedidos. Resolva os outros primeiro.</t>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Parece que você já pegou muitos pedidos. Resolva os outros primeiro.</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -877,9 +877,9 @@
           <t>questInProgress</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Está tudo bem com sua tarefa?</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Está tudo bem com a sua tarefa?</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -899,9 +899,9 @@
           <t>questComplete</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Ah, vejo que concluiu meu pedido! Obrigado. Aqui está sua recompensa.</t>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Oh, vejo que terminou meu pedido! Obrigado. Aqui está sua recompensa.</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -921,9 +921,9 @@
           <t>bird1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Ah, eu adoro observar os pássaros!</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Ah, adoro observar pássaros!</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -943,10 +943,10 @@
           <t>bird2</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Okay, agora não tem mais volta!_x000D_
-Vamos lá!</t>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Beleza, sem volta agora!
+Vamos!</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -968,9 +968,9 @@
           <t>bird3</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Certo, docinho, preciso de #1 Orens na frente.</t>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Beleza querido, preciso de #1 orens adiantado.</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -990,9 +990,9 @@
           <t>blooming1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Hmph, seu companheiro parece bem amadurecido de fato. O laço que você cultivou através de suas viagens está pronto para florescer. Talvez eu deva ajudar nisso...</t>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Hmph, seu companheiro parece bem maduro mesmo. O vínculo que você cultivou nas viagens está pronto para florescer. Talvez eu o ajude a desabrochar...</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -1012,7 +1012,7 @@
           <t>blooming2</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Muwohohohohohoho, FLORESÇA!</t>
         </is>
@@ -1034,9 +1034,9 @@
           <t>blooming3</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Muwohoho. Sua sinceridade decidirá meu favor. Me encante, se você ousar.</t>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Muwohoho. Sua sinceridade decidirá meu favor. Encante-me, se tiver coragem.</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1056,9 +1056,9 @@
           <t>tail1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Você é... bastante atraente. Eu vou te comprar.</t>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Você é... bem atraente. Vou te comprar.</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -1078,10 +1078,10 @@
           <t>tail2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Okay, agora não tem mais volta!_x000D_
-Vamos lá!</t>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Beleza, sem volta agora!
+Vamos!</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
@@ -1103,9 +1103,9 @@
           <t>tail3</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Certo, docinho, preciso de #1 Orens na frente.</t>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Beleza querido, preciso de #1 orens adiantado.</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -1125,7 +1125,7 @@
           <t>tail4</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Por que está me olhando, #pc?</t>
         </is>
@@ -1147,9 +1147,9 @@
           <t>lockpick_purse</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Provavelmente um objeto perdido. Mas ei, será que me importo?</t>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Provavelmente um objeto perdido. Mas, ei, eu ligo?</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -1169,9 +1169,9 @@
           <t>invite</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Quer que eu me mude para sua casa?</t>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Quer que eu me estabeleça no seu lar?</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -1191,7 +1191,7 @@
           <t>invite2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Infelizmente, não posso me juntar a você agora.</t>
         </is>
@@ -1213,9 +1213,9 @@
           <t>invite3</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Se você fosse só um pouquinho mais carismático, quem sabe.#newline(#1 de carisma necessário)</t>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Se você fosse só um pouquinho mais charmoso, talvez.#newline(#1 de carisma necessários)</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -1235,9 +1235,9 @@
           <t>inviteReq1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Você pode me dar #1?</t>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Pode me dar #1?</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -1257,7 +1257,7 @@
           <t>talk_hobby</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Meu hobby é #1.</t>
         </is>
@@ -1279,9 +1279,9 @@
           <t>talk_fav</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Meu favorito? Gosto de #1 e tenho uma quedinha por #2.</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Meu favorito? Gosto de #1 e tenho uma fraqueza por #2.</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -1301,9 +1301,9 @@
           <t>slave_buy</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Você quer #2? Oh, você tem um gosto refinado! Vai te custar #1 Orens.</t>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Quer #2? Oh, você tem bom gosto! Vai custar #1 orens.</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
@@ -1323,9 +1323,9 @@
           <t>slave_buy2</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>#1 é seu a partir de agora. Cuide bem do seu novo pet.</t>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>#1 é seu a partir de agora. Cuide bem do seu novo bicho.</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
@@ -1345,9 +1345,9 @@
           <t>goto</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>#1? Sim, deixe-me te mostrar onde ele estava.</t>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>#1? Sim, te mostro onde ele estava.</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
@@ -1367,9 +1367,9 @@
           <t>goto2</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Boa piada.</t>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Piada engraçada.</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -1389,9 +1389,9 @@
           <t>upgrade_heath1</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Precisaremos de #1 para aprimorar a Pedra do Lar até o nível #2.#3</t>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>Precisaremos de #1 para elevar a pedra do lar ao nível #2.#3</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
@@ -1411,9 +1411,9 @@
           <t>upgrade_heath2</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Ótimo, isso deve ajudar nosso lar a evoluir ainda mais!</t>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Ótimo, isso vai ajudar nosso lar a avançar ainda mais!</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -1433,9 +1433,9 @@
           <t>invest1</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Interessado em investir? Você já investiu #2 Orens até agora e #zone está buscando um investimento de #1 Orens.</t>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Interessado em investir? Você já investiu #2 orens e #zone agora busca #1 orens de investimento.</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -1455,7 +1455,7 @@
           <t>invest2</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Obrigado! Seu investimento tornará #zone mais próspera.</t>
         </is>
@@ -1477,9 +1477,9 @@
           <t>invest_shop1</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Oh, quer investir na minha loja? Vai te custar #1 Orens. Espero que tenha o dinheiro.</t>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Oh, quer investir na minha loja? Vai custar #1 orens. Espero que tenha o dinheiro.</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
@@ -1499,9 +1499,9 @@
           <t>invest_shop2</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Você salvou o meu dia!</t>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Você fez meu dia!</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -1521,9 +1521,9 @@
           <t>questCompleteDeliver</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Oh, você trouxe o que pedi, #1! Muito obrigado. Aqui está sua recompensa.</t>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Oh, você me trouxe #1! Obrigado. Aqui está sua recompensa.</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
@@ -1543,9 +1543,9 @@
           <t>questCompleteDeliverExtra</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Ah, este é certamente o item que eu pedi. Vou te dar uma recompensa digna de #1.</t>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oh, este é certamente o item que pedi. Vou te dar uma recompensa digna de #1. </t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
@@ -1565,9 +1565,9 @@
           <t>miral_medal</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Ho ho ho! Você trouxe medalhas pequenas! Deixe-me ver, deixe-me ver! Gostaria de trocá-las por uma das minhas obras-primas?</t>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Ho ho ho! Você tem medalhinhas! Deixa ver, deixa ver! Quer trocá-las por uma das minhas obras de orgulho?</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
@@ -1587,9 +1587,9 @@
           <t>miral_medal2</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Humpf!</t>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Hump!</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
@@ -1609,9 +1609,9 @@
           <t>shop_criminal</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Não faço negócios com criminosos.</t>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Não faço negócios com criminais.</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
@@ -1631,9 +1631,9 @@
           <t>shop_blackmarket_noaccess</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Heh, que negócio um aventureiro tão certinho como você tem comigo?</t>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>Heh, que negócio um aventureiro certinho como você tem comigo?</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -1653,9 +1653,9 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Está procurando por alguém?</t>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Procurando alguém?</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
@@ -1675,7 +1675,7 @@
           <t>shutup</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>(#tg para de falar...)</t>
         </is>
@@ -1697,7 +1697,7 @@
           <t>shutup2</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>(#tg te abraça.)</t>
         </is>
@@ -1719,9 +1719,9 @@
           <t>insult</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Você é um pervertido sem salvação.</t>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Você é um pervertido sem conserto.</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -1741,9 +1741,9 @@
           <t>insult2</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Parece que você finalmente voltou ao normal.</t>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Parece que você finalmente ficou normal.</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
@@ -1763,9 +1763,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>(#tg faz um leve aceno com a cabeça.)</t>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>(#tg dá um aceno de cabeça.)</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -1785,9 +1785,9 @@
           <t>refuse</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>(#tg recusa gentilmente sua proposta.)</t>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>(#tg recusa sua proposta com gentileza.)</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
@@ -1807,9 +1807,9 @@
           <t>deliver_purse</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Que gentileza a sua em se dar ao trabalho de trazer isso. Você é um verdadeiro exemplo de cidadania!</t>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Que gentileza sua dar esse trabalho de trazer. Você é um cidadão exemplar, de verdade!</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
@@ -1829,9 +1829,9 @@
           <t>news1</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Há um lugar chamado #1 aqui por perto. Se estiver interessado, talvez valha a pena explorar.</t>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Há um lugar chamado #1 por aqui. Se estiver interessado, pode valer a pena explorar. </t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
@@ -1851,9 +1851,9 @@
           <t>news2</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Infelizmente, não tenho boas notícias no momento.</t>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Infelizmente, não tenho boas notícias agora.</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
@@ -1873,11 +1873,11 @@
           <t>bout1</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Quer testar sua força?_x000D_
-Está falando sério?_x000D_
-Está querendo arrumar confusão comigo?</t>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Quer testar sua força?
+Está falando sério?
+Está me provocando?</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -1901,11 +1901,11 @@
           <t>bout2</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Muito bem, você tem coragem!_x000D_
-Isso sim é espírito!_x000D_
-Certo, vamos ver do que você é capaz!</t>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muito bem, essa coragem é boa!
+Esse é o espírito!
+Vamos ver do que você é capaz! </t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -1929,9 +1929,9 @@
           <t>what</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>O quê?</t>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Que?</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -1951,9 +1951,9 @@
           <t>becomeMaid</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Certo, serei sua empregada a partir de hoje.</t>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>Beleza, sou sua empregada a partir de hoje.</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -1973,9 +1973,9 @@
           <t>sellFame1</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Ha ha, #brother, está assim tão desesperado por dinheiro? Tudo bem, comprarei sua reputação por #1 Orens.</t>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ha ha, #brother, está tão desesperado por dinheiro? Beleza, compro sua reputação por #1 orens. </t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
@@ -1995,9 +1995,9 @@
           <t>sellFame2</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Valeu, farei bom uso da sua reputação.</t>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>Obrigado, vou fazer bom uso da sua reputação.</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
@@ -2017,9 +2017,9 @@
           <t>blessing</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Deseja ser abençoado? Muito bem, incline a cabeça!</t>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Deseja ser abençoado? Muito bem, curve a cabeça!</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -2039,9 +2039,9 @@
           <t>lockTooHard</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Essa fechadura parece complicada demais pra mim. Desculpe, mas vai ter que lidar com isso sozinho.</t>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Este cofre parece complicado demais para mim. Desculpa, mas você vai ter de resolver sozinho.</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -2061,9 +2061,9 @@
           <t>loytel_bill_give1</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Claro... Agradeço por me ajudar com o pagamento da dívida. Vamos lidar com essa pequena conta primeiro. Jogue-a no baú de impostos e me avise quando o pagamento estiver concluído.</t>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Claro... Agradeço por me ajudar a pagar minha dívida. Muito bem, vamos resolver esta primeira nota de dívida. Jogue-a no baú de impostos e me reporte quando o pagamento estiver completo.</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
@@ -2083,9 +2083,9 @@
           <t>loytel_bill_give2</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Claro... Me dói te entregar isto, mas aqui está a próxima conta. Venha falar comigo novamente quando terminar o pagamento.</t>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Claro... Dói me entregar isto, mas aqui vai a próxima nota. Venha falar comigo de novo quando terminar de pagar.</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
@@ -2105,9 +2105,9 @@
           <t>loytel_bill_give_given</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Você está com o título da dívida. Ele é importante, por favor, não o perca.</t>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Você tem a nota de dívida. Ela é importante, então não a perca, por favor.</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -2127,9 +2127,9 @@
           <t>loytel_bill_give_wait</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Ainda não estou pronto para a próxima conta... Pode esperar mais um pouco?</t>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ainda não estou pronto para a próxima nota... Pode esperar mais um pouco? </t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -2149,9 +2149,9 @@
           <t>loytel_bill_give_lost</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>... Lembra quando eu disse "Não o perca"? Aqui está outro, então cuide bem dele desta vez.</t>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>...Lembra quando eu disse, "Não perca"? Aqui vai outra, então cuida dela desta vez.</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -2171,9 +2171,9 @@
           <t>marry</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Sim... com prazer.</t>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>Sim...com prazer.</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -2193,9 +2193,9 @@
           <t>wedding_deed</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Isso me deixa feliz. Mas precisamos de uma Permissão de Casamento.</t>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Isso me deixa feliz. Mas precisamos de uma Licença de Casamento.</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -2215,7 +2215,7 @@
           <t>wedding_zone</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Isso me deixa feliz. Mas vamos com calma e conversar em casa.</t>
         </is>
@@ -2237,9 +2237,9 @@
           <t>wedding_confirm</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Está falando sério? (Seu grupo atual será dissolvido, e um novo grupo será formado apenas com você e #tg.)</t>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Está falando sério? (Seu grupo atual é dissolvido, e um novo grupo se forma só com você e #tg.)</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -2259,9 +2259,9 @@
           <t>wedding_accept</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Estou tão feliz, #pc! Estou realmente feliz.</t>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>Estou tão feliz, #pc! Estou feliz de verdade.</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -2272,6 +2272,170 @@
       <c r="D88" s="17" t="inlineStr">
         <is>
           <t>I'm so happy, #pc! I'm truly happy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="74.59999999999999" customHeight="1" s="14">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>rob1</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Errei sobre você!
+Por favor, pare com isso!
+Você vai se arrepender de vir atrás de mim.
+O que faz pensar que um bandido comum pode comigo?
+Por favor, pare. Você vai se arrepender.
+Mercenários, expulsem esse cafajesto.
+Hmph. Não vê quantos guardas eu tenho?</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>見損なった{よ}！
+ひどい{よ}、やめて{くれ}！
+返り討ちにしてくれる{よ}。
+ごろつき風情に何ができるという{のだ}？
+やめて{くれ}。きっと後悔する{よ}。
+傭兵さんたち、このごろつきを追い払って{くれ}。
+ふん、この護衛の数が見えないの{か}？</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>I misjudged you!
+Please, stop this!
+You'll regret coming after me.
+What makes you think a common thug can take me on?
+Please stop. You'll regret this.
+Mercenaries, drive this ruffian off.
+Hmph. Can't you see how many guards I have?</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32.8" customHeight="1" s="14">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>mama_yes</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>A mamãe está aqui!
+Sim, eu sou sua mamãe!
+A mamãe está bem aqui.</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>ママだよ！
+{はい}、ママ{だ}～！
+ママはここにいる{のだ}。</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Mommy's here!
+Yes, I'm your mommy!
+Mommy is right here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="64.15000000000001" customHeight="1" s="14">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>mama_no</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xô, xô!
+Não sou sua mãe!
+Do que você está falando...?
+Que pena... bateu a cabeça?
+Que assustador...
+Hã...? </t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>シッシッ！
+ママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+気持ち悪い{よ}…
+え…？</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shoo, shoo!
+I'm not your mom!
+What are you talking about...?
+How pitiful... did you hit your head?
+That’s creepy...
+Huh...? </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32.8" customHeight="1" s="14">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>baby_yes</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>Mamãe!
+...Você é minha...mamãe?
+Mã... mama...?</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>ママー！
+私の…ママなの{か}？
+マ…ママ…？</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Mommy!
+...You are my...mommy?
+Ma... mama...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="43.25" customHeight="1" s="14">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>baby_no</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você não é minha mamãe!
+Do que você está falando...?
+Que pena... bateu a cabeça?
+Hã...? </t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>こんなのママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+え…？</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You're not my mommy!
+What are you talking about...?
+How pitiful... did you hit your head?
+Huh...? </t>
         </is>
       </c>
     </row>
@@ -2334,15 +2498,15 @@
           <t>default</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não tenho nada para fazer. 
-Hã? O que você quer?  
-Você é um aventureiro, certo? Alguma novidade?  
-A Liga Eterna? Nunca ouvi falar.  
-Nada supera uma boa e velha cerveja depois do trabalho.  
-Gatos... Por que eles são tão fofos?  
-#aka? Nunca ouvi falar de você.  </t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Não tenho nada para fazer.
+Hã? O que você quer?
+Você é aventureiro, né? Tem notícias de longe?
+A Liga Eterna? Nunca ouvi falar.
+Nada supera uma cerveja de crim depois do trabalho.
+Gatos... por que são tão fofos?
+#aka? Nunca ouvi falar de você.</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -2374,12 +2538,12 @@
           <t>interest_economy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eu gosto muito de economia.  
-De qualquer forma, dinheiro é o mais importante nesse mundo.
-Você tem boas ideias de investimento?  
-Moedas de platina são muito mais raras que as de ouro. Gaste-as com sabedoria.  </t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Sou muito fã de economia.
+Dinheiro e moeda são cruciais para a nossa sociedade.
+Tem boas ideias de investimento?
+Moedas de platina são bem mais raras que ouro. Gaste com sabedoria.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2405,12 +2569,12 @@
           <t>interest_science</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gosto de falar sobre ciência.  
-A ciência em Eyth Terre era muito mais avançada que a nossa.  
-Em Eyth Terre, magia e ciência eram consideradas opostas.  
-Dizem que bonecos mecânicos estão fazendo o trabalho dos humanos no Novo Reino de Yerl.  </t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Gosto de falar de ciência.
+A ciência em Eyth Terre era muito mais avançada que a nossa.
+Em Eyth Terre, magia e ciência eram tidas como opostos.
+Dizem que marionetes mecânicas fazem o trabalho dos humanos no Novo Reino de Yerl.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2436,12 +2600,12 @@
           <t>interest_travel</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Gosto de viajar, já estive em muitos lugares.  
-Lumiest é a famosa cidade da arte.  
-As terras de North Tyris têm inúmeras ruínas e masmorras. Elas são chamadas de ruínas de Nefia.  
-Se for viajar, é bom levar bastante comida consigo.</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Gosto de viajar, já fui a tantos lugares.
+Lumiest é a famosa cidade da arte.
+A terra de Tyris do Norte tem incontáveis ruínas e masmorras. Elas se chamam ruínas de Nefia.
+Você nunca deve sair de casa sem um bom suprimento de comida.</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2467,12 +2631,12 @@
           <t>interest_world</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tenho interesse na situação mundial.  
-Euderna é um poderoso império nos desertos do continente oriental.  
-Dizem que o Novo Reino de Yerl foi fundado por escravos que fugiram do império.  
-Zanan é um antigo reino que valoriza a história e a honra, mas aparentemente é um fantoche do império.  </t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Me interesso pelos assuntos do mundo.
+Euderna é um império poderoso nos desertos do continente oriental.
+Dizem que o Novo Reino de Yerl foi fundado por escravos que fugiram do império.
+Zanan é um reino antigo que valoriza história e honra, mas aparentemente é um fantoche do império.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2498,15 +2662,15 @@
           <t>interest_religion</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A fé é a mais preciosa de todas.  
-Nossas vidas seriam sem sentido sem os deuses.  
-Dizem que as penas que caem das pequenas asas na cabeça da Deusa da Cura têm o poder de curar qualquer doença incurável.  
-A terra treme às vezes porque Opatos está se virando.  
-Não consigo dormir à noite pensando se Kumiromi é Deus ou Deusa!  
-Você diz que a Deusa da Fortuna é um gato? Hahaha, que bobagem!  
-Corre um boato de que Mani da Máquina foi, originalmente, humano.  </t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>A fé é o mais precioso de tudo.
+Nossas vidas não teriam sentido sem os deuses.
+Dizem que as penas que caem das pequenas asas na cabeça da Deusa da Cura têm o poder de curar qualquer doença incurável.
+A terra treme às vezes porque Opatos está se virando na cama.
+Não durmo à noite pensando se Kumiromi é Deus ou Deusa!
+Você disse que a Deusa da Sorte é uma gata? Hahaha, absurdo!
+Corre rumor de que Mani da Máquina era originalmente humano.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2538,12 +2702,12 @@
           <t>interest_human</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Os Elea tentaram nos abandonar à própria sorte durante a Guerra dos Dez Anos.  
-Chegou a hora de nós, humanos, prosperarmos.  
-Não precisamos mais da ajuda dos Elea.  
-As florestas onde os Elea vivem deveriam ser todas queimadas.</t>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Os Elea tentaram nos deixar na miséria na Guerra dos Dez Anos.
+Chegou a hora de nós, humanos, prosperarmos.
+Não precisamos mais de ajuda dos Elea.
+Queimem as florestas antigas!</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2569,12 +2733,12 @@
           <t>interest_elea</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Os humanos precisam ser mais humildes. Devem respeitar as raças antigas.
-Antigamente, os humanos chamavam os Elea de mães.  
-O povo das antigas florestas não gosta de lutar. Eles não querem Parece que o povo da floresta não quer interferir e nem ser incomodado.  
-Por que não podemos simplesmente deixar os Elea em paz?  </t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Os humanos precisam ser mais humildes. Devíamos respeitar mais as raças mais velhas.
+Os humanos um dia chamaram os Elea de mãe.
+O povo das florestas antigas não gosta de brigar. Não querem interferir nem ser interferidos.
+Por que não podemos deixar os Elea em paz?</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2600,17 +2764,17 @@
           <t>shopkeeper</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bem-vindo. Dê uma olhada com calma.
-Tenho confiança nos produtos que vendo.
-Gerenciar uma loja não é nada fácil.
-Se não for forte o bastante pra espantar bandidos, não dá pra ser dono de loja.
-Em outras lojas, é bom tomar cuidado pra não ser passado pra trás.
-Já tenho alguém escolhido para herdar a loja quando for preciso.
-Vamos lá, veja meus produtos com orgulho.
-Ultimamente tem aparecido muita gente perigosa, tá difícil.
-Armas e armaduras só são bem compradas se forem devidamente avaliadas.</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Bem-vindo à minha loja!
+Temos a melhor seleção de mercadorias!
+Comandar uma loja é trabalho duro!
+Bandoleros eu resolvo sozinha. Temos de ser durona.
+Entre. Olhe de perto minhas mercadorias.
+Confio no meu sortimento de produtos.
+Veja nossa bela seleção.
+Sinto o mundo ficando cada vez mais perigoso.
+Não posso dar preço justo se suas armas e armaduras não estiverem totalmente identificadas.</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2646,10 +2810,11 @@
           <t>guard</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O trabalho da guarda é proteger a segurança dos cidadãos.  
-Se vir alguém suspeito, avise.  </t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>É nosso dever proteger os cidadãos.
+Me reporte se vir qualquer suspeito.
+Eu era um aventureiro como você, até que...</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2673,11 +2838,11 @@
           <t>banker</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seu dinheiro é mais importante do que qualquer outra coisa.  
-Há coisas que o dinheiro não pode comprar.  
-Bem-vindo ao nosso banco!  </t>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Seu dinheiro é mais importante que qualquer coisa.
+Há coisas que dinheiro não compra.
+Bem-vindo ao nosso banco!</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -2701,9 +2866,9 @@
           <t>bitch</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ah~ meu bem, que #gender encantador{だ}。Deixe-me te dar um sonho inesquecível esta noite.</t>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Ei, gato, quer relaxar um pouco?</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -2723,10 +2888,10 @@
           <t>slaver</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você também não parece ser flor que se cheire, hein.
-Não me olhe assim.  </t>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>He he he. Acho que tenho exatamente o que você precisa.
+Não olhe para mim assim.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -2748,10 +2913,10 @@
           <t>bored</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(#me parece entediado.)  
-(#me lançou um olhar e virou o rosto.)  </t>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>(#me parece entediado. )
+(#me olha para você e dá um passo atrás.)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -2775,25 +2940,25 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dizem que caudas de coelho trazem boa sorte para quem as come.  
-Não subestime o lançador de pedras. As pedras dele podem ser mortais.  
-Encontrei meu deus em um sonho!  
-Alguns nobres colecionam coisas estranhas.  
-Cuidado com os bêbados nas festas! Às vezes, eles jogam coisas absurdas em você.  
-Aqueles ladrões miseráveis, ouvi dizer que são viciados em algumas drogas.  
-Um mago viajante grelhou carne com magia de fogo para mim. Para ser sincero, ficou mais saborosa do que a de muitos lugares!  
-Não consegue cavar a rocha? Por que não tenta fazer uma picareta com um material mais resistente?  
-Dizem que em algum lugar deste continente existe uma árvore gigante onde fadas vivem.  
-Não pagar seus impostos pode te meter em sérios problemas, sabia?  
-Acredite em mim! Eu vi um putit dourado da neve com meus próprios olhos!  
-Ouvi falar de uma lâmpada que brilha com a luz do sol.  
-Se você pegar um peixe grande, não seria um desperdício simplesmente vendê-lo como está?  
-Sabia que você absorve mais nutrientes quando está com fome?  
-Se quiser coletar ervas, tente explorar as florestas de Nefia.  
-Se treinar sua natação, isso aumentará sua resistência!  
-Dizem que os gourmets conseguem até identificar quais cogumelos são venenosos.  
-O informante pode abrir um baú de tesouro trancado para você.  
-Se achar os pedidos difíceis, uma opção é vender sua fama.  </t>
+          <t>Rabo de coelho, dizem, dá sorte a quem o come.
+Não subestime o arremessador de pedras. A pedra dele pode ser mortal.
+Conheci meu deus num sonho!
+Alguns nobres colecionam coisas estranhas.
+Cuidado com bêbados em festas! Às vezes eles jogam coisas malucas em você.
+Aqueles desgraçados ladrões, ouvi dizer que são viciados em algumas drogas.
+Uma maga viajante grelhou carne com magia de fogo para mim. Sinceramente, estava mais gostoso que na maioria dos lugares!
+Não consegue cavar a pedra? Por que não tenta fazer uma picareta com material mais duro?
+Em algum lugar deste continente, dizem que há uma árvore gigante onde fadas vivem.
+Não pagar seus impostos pode te enfiar numa encrenca séria, sabia.
+Acredite! Vi um putit de neve dourado com meus próprios olhos!
+Ouvi dizer que há uma lâmpada que brilha com a luz do sol.
+Se pescar um peixe grande, seria desperdício vendê-lo como está, não?
+Sabia? Você na verdade absorve mais nutrientes se estiver com fome.
+Se quiser colher ervas, tente explorar as florestas de Nefia.
+Se treinar sua natação, isso fortalece seu vigor!
+Os gourmet, ouvi dizer, conseguem até dizer quais cogumelos são venenosos.
+O informante pode abrir um baú trancado para você.
+Se achar os pedidos difíceis, uma opção é vender sua fama.</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -2850,24 +3015,24 @@
           <t>fortune</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se você adorar Kumiromi, pode encontrar sementes em carne podre.  
-Nunca desperdice kits de materiais em itens comuns!  
-Comida rica em nutrientes tem um valor real se você alimentá-la ao seu pet.  
-Melhores ferramentas trazem melhores resultados para suas habilidades. Melhores camas trazem melhores sonhos se você dormir nelas.  
-Você terá mais chances de acertos críticos contra oponentes atordoados.  
-Enquanto estiverem envenenados, sangrando ou paralisados, seus oponentes não se regenerarão.  
-Os cubos não se dividirão quando estiverem em más condições.  
-Você pode usar um pergaminho de reconstrução em um artefato para recriá-lo.  
-Você pode evitar ser atordoado aumentando sua resistência ao som.  
-Você pode evitar ficar insano aumentando sua resistência à mente.  
-Abençoar uma vara mágica é uma boa ideia. Mas os efeitos das varas abençoadas são menos dramáticos do que os das poções ou pergaminhos abençoados.  
-Quando você está molhado, danos de fogo não serão um problema, mas danos elétricos serão uma ameaça séria.  
-Se vomitar muito em um curto período, sofrerá de anorexia. Quando tiver anorexia, não coma. Apenas beba poções e água.  
-Uma poção abençoada de restauração do corpo ou do espírito fortalecerá seu corpo ou espírito.  
-Jogue poções amaldiçoadas de restauração do corpo ou do espírito em oponentes poderosos.  
-Se você tiver a habilidade de natação, poderá atravessar para outro continente nadando.  </t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Se cultuar Kumiromi, pode achar sementes em carne podre.
+Nunca desperdice kits de material em itens comuns!
+Comida densa em nutrientes vale muito se alimentar seu bicho.
+Ferramentas melhores dão resultados melhores às suas perícias. Camas melhores dão sonhos melhores se você dormir nelas.
+Você terá mais chances de acertos críticos contra oponentes atordoados.
+Envenenado, sangrando ou paralisado, seu oponente não regenera.
+Os cubos não se dividem quando estão em más condições.
+Você pode usar um pergaminho de reconstrução num artefato para recriar o artefato.
+Você pode evitar ficar atordoado aumentando sua resistência a som.
+Você pode evitar enlouquecer aumentando sua resistência a mente.
+Abençoar uma varinha é boa ideia. Mas os efeitos de varinhas abençoadas são menos dramáticos que poções ou pergaminhos abençoados.
+Quando você está molhado, dano de fogo deixa de ser problema, mas dano elétrico vira ameaça séria.
+Se vomitar demais em pouco tempo, sofrerá anorexia. Quando pegar anorexia, não coma. Só beba poções e água.
+Uma poção abençoada de restaurar corpo ou espírito aprimora seu corpo ou espírito.
+Arremesse poções amaldiçoadas de restaurar corpo ou espírito em oponentes poderosos.
+Com a perícia de natação, você pode nadar até outro continente.</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -2900,8 +3065,8 @@
 While poisoned, bleeding, or paralyzed, your opponent won't regenerate. 
 The cubes will not split when they have bad conditions.
 You can use a scroll of reconstruction to an artifact to re-create the artifact.
-You can prevent getting dimmed by increaseing your resistance to sound.
-You can prevent getting insane by increaseing your resistance to mind.
+You can prevent getting dimmed by increasing your resistance to sound.
+You can prevent getting insane by increasing your resistance to mind.
 Blessing a rod is a good idea. But the effects of blessed rods are less dramatic than blessed potions or scrolls.
 When you are wet, fire damages won't be a problem but electric damages will be a serious threat.
 If you vomit too much in a short period, you will suffer anorexia. When you get anoerxia, don't eat. Just drink potions and water.
@@ -2917,19 +3082,31 @@
           <t>fortune_false</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Um anel de dedo extra é inútil se não for encantado.  
-Um cajado pode recarregar se você deixá-lo no chão por um tempo.  
-Não sabe o que desejar? Experimente "artefato secreto de Milas".  
-Gemas podem ser trocadas por moedas de platina.  
-Sempre abençoe os mapas do tesouro antes de lê-los.  
-Meo... eow...  
-O que você deseja?  
-Se você gritar 'Guardas!' na janela de chat, eles podem vir ajudá-lo rapidamente.  
-Há um jeito de fazer um Deus seu mascote.  
-Assassinos de jogadores aguardam você ao entrar nos Moongates.  
-Oh, que pena. Odeio dizer isso, mas q+B19+B21+B19+B21</t>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Um anel de dedo extra é inútil se não for encantado.
+Um cajado pode recarregar se você o largar por um tempo.
+Sem certeza do que desejar? Tente o artefato secreto de Milas.
+Gemas podem ser trocadas por moedas de platina.
+Sempre abençoe os mapas do tesouro antes de ler.
+Meo....miau.....
+O que você deseja?
+Se gritar 'Guardas!' na janela de chat, eles podem vir rápido te ajudar.
+Há um jeito de fazer um Deus seu bicho.
+Assassinos de jogadores te esperam quando você entra nos portões da lua.
+Ah, que pena. Desgosta-me dizer, mas quem ler esta fortuna *será* amaldiçoado.
+Cuidado pelas costas! Atenção! L-Lá, sua irmãzinha! Corra!
+Nyo BUMP-BUMP para você!
+O jogo não pôde escolher fortunas válidas pois seu jogo salvo está corrompido.
+Corre rumor de que matar gatos dá azar.
+Os guardas ficarão contentes se espancá-los pelado.
+Corre rumor de que há um artefato supremo exclusivo para suas irmãzinhas.
+Um rancho perto de Derphy pode ser bem lucrativo.
+O imposto cai se seu karma estiver alto.
+Os lojistas pagam mais por merda de monstro que pese mais.
+Beber poções de cura amaldiçoadas às vezes te deixa doente.
+Você *deve* abençoar o sangue de Hermes antes de bebê-lo!
+Seria muito ruim se algo desse errado quando você conjurar o feitiço de retorno.</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -2980,7 +3157,7 @@
 It is rumored that there's an ultimate artifact exclusive to your younger sisters.
 A ranch near Derphy can be highly profitable. 
 Tax will be lowered if your karma is high.
-Shopkeepers will pay more for monster's shit that weights more.
+Shopkeepers will pay more for monster shit that weighs more.
 Drinking cursed healing potions sometimes makes you sick.
 You *should* bless the hermes blood before drinking it!
 It would be really bad if something wrong happenes when you cast the return spell.</t>
@@ -2993,11 +3170,11 @@
           <t>mayor</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode falar com minha secretária se precisar de documentos.  
-O que você quer? Estou bastante ocupado.  
-Investimentos na cidade são sempre bem-vindos.  </t>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Se precisar de papelada, fale com minha secretária.
+O que você quer? Estou bem ocupado.
+Investimentos na cidade são sempre bem-vindos.</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -3021,10 +3198,10 @@
           <t>secretary</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gostaria de investir na cidade?  
-Como posso servi-lo hoje?  </t>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Gostaria de investir na cidade?
+Como posso servi-la hoje?</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -3040,61 +3217,38 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="231.3" customHeight="1" s="14">
+    <row r="24" ht="252.2" customHeight="1" s="14">
       <c r="A24" s="18" t="inlineStr">
         <is>
           <t>bottle</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lucia|O Navio Que Nunca Retornou|Se esta garrafa chegar a alguém, provavelmente já estarei sob o mar.
-Mas o céu estava muito azul.
-Um Soldado Anônimo|Carta Final|O medo pesava mais que minha espada.
-Mas quero que alguém saiba que não fugi.
-Ernes|Prece das Ondas|Deus, se não puder acalmar as ondas,
-então ao menos me conceda o sono.
-Mireille|A Praia Prometida|Se eu chegar primeiro,
-acenderei uma fogueira e esperarei.
-Venha sem se perder.
-Navegador Daros|Registro das Estrelas|As estrelas estavam corretas hoje.
-Quem errou fui eu.
-Selena|Uma Pequena Confissão|Eu nunca consegui dizer seu nome em voz alta.
-Esse é meu único arrependimento.
-Velho|Aos Meus Dias Mais Jovens|O mar toma muito,
-mas nada é inteiramente desperdiçado.
-Sobreviva.
-O Gêmeo Mais Novo|Metade do Mundo Ficou|Irmão, metade do mundo ainda está aqui.
-Então, por favor, volte.
-Médico de Bordo Renato|Anotações Médicas|Não consegui curar as feridas,
-mas aliviei a dor.
-Isso foi o suficiente.
-Isabelle|Termine a Canção|Mesmo que eu não esteja mais aqui,
-por favor, cante esta canção até o fim.
-Contrabandista Kyle|Onde Está o Pagamento|O ouro está afundado na enseada ao norte.
-Mergulhe se quiser.
-Acolita Roa|Confissão de Dúvida|Minhas preces não foram respondidas.
-Ainda assim, não pararei de rezar.
-Pescador Hald|A Última Pescaria|Não houve pesca hoje.
-Mas conversei com o mar.
-Viajante Cyan|Um Ponto de Passagem|Este não é o fim.
-É apenas um ponto de passagem.
-Escriba Real|Trecho dos Registros Oficiais|A embarcação foi perdida na tempestade.
-Fim do relatório.
-Mãe|Para Meu Filho|Coloque seu manto quando esfriar.
-Prometa.
-Bardo Fey|Um Poema Inacabado|A rima está faltando.
-Para quem o terminar.
-Capitão Mercenário Volk|Ordem de Retirada|Voltem vivos.
-A honra pode ser recuperada depois.
-Garotinha|Minha Primeira Viagem|Estou com um pouco de medo.
-Mas é divertido.
-Alguém|Para Quem Encontrar Isto|Se está lendo isto,
-o mundo ainda continua.
-Desconhecido|Eu...
-Estou... indo... para casa...!
-Desconhecido|Eu estou...
-Moudamepo</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Lucia|O Navio que Nunca Voltou|Se esta garrafa alcançar alguém, provavelmente estarei sob o mar quando isso acontecer. Mas o céu estava muito azul.
+Um Soldado Sem Nome|Carta Final|O medo pesava mais que minha espada. Mas quero que alguém saiba que eu não fugi.
+Ernes|Oração das Ondas|Deus, se não podes acalmar as ondas, então pelo menos me concede o sono.
+Mireille|A Orla Prometida|Se eu chegar primeiro, acenderei uma fogueira e esperarei. Venha sem perder o caminho.
+O navegador Daros|Registro das Estrelas|As estrelas estavam certas de novo hoje. Quem errou fui eu.
+Selena|Uma Pequena Confissão|Eu nunca pude dizer seu nome em voz alta. Esse é meu único arrependimento.
+O Velho|Para Meus Dias Moços|O mar leva muito, mas nada é totalmente perdido.Sobreviva.
+O Gêmeo Mais Novo|Metade do Mundo Restante|Irmão, metade do mundo ainda está aqui. Então por favor volte.
+O médico de bordo Renato|Notas Médicas|Não pude curar as feridas, mas aliviei a dor. Isso bastou.
+Isabelle|Terminem a Canção|Mesmo que eu tenha partido, cantem esta canção até o fim.
+O contrabandista Kyle|Onde Está o Pagamento|O ouro está afundado na enseada norte. Mergulhe se quiser.
+O acólito Roa|Confissão de Dúvida|Minhas orações não foram respondidas. Ainda assim, não pararei de orar.
+O pescador Hald|A Última Pesca|Não houve pesca hoje. Mas eu conversei com o mar.
+A viajante Cyan|Um Ponto de Passagem|Isto não é o fim. É só um ponto de passagem.
+O escriba real|Trecho dos Registros Oficiais|A embarcação foi perdida para a tempestade. Fim do relato.
+Mãe|Para Meu Filho|Vista a capa quando esfriar. Prometa.
+A bardo Fey|Um Poema Inacabado|Falta a rima. Para quem a terminar.
+A capitã mercenária Volk|Ordem de Recuo|Voltem vivos. A honra pode ser recolhida depois.
+A garotinha|Minha Primeira Viagem|Estou com um pouquinho de medo. Mas é divertido.
+Alguém|Para Quem Encontrar Isto|Se você está lendo isto, o mundo ainda continua.
+Desconhecido|Eu...|Eu...vou...pra...casa...!
+Desconhecido|Eu sou...|Moudamepo
+O Rei dos Piratas|Meu tesouro?|Achem! Deixei tudo o que tenho neste mundo lá!
+O pirata|Me vejam|Eu serei o Rei dos Piratas!!</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -3120,33 +3274,37 @@
 少女|はじめての旅|少し怖い。でも楽しい。
 誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
 不明|お…|おうち…かえう…！
-不明|もう…|もうだめぽ</t>
+不明|もう…|もうだめぽ
+海賊王|財宝| 探せ！ この世の全てをそこに置いてきた！
+海賊|見てろ！| 海賊王に、おれはなる ！！</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Lucia|The Ship That Never Returned|If this bottle reaches someone,I will likely be beneath the sea by then.But the sky was very blue.
-An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword.But I want someone to know I did not run.
-Ernes|Prayer of the Surf|God,if you cannot calm the waves,then at least grant me sleep.
-Mireille|The Promised Shore|If I arrive first,I will light a fire and wait.Come without losing your way.
-Navigator Daros|Record of the Stars|The stars were correct again today.The one who erred was me.
-Selena|A Small Confession|I could never speak your name aloud.That is my only regret.
-Old Man|To My Younger Days|The sea takes much,but nothing is entirely wasted.Survive.
-The Younger Twin|Half the World Left|Brother,half the world is still here.So please come back.
-Ship Doctor Renato|Medical Notes|I could not heal the wounds,but I eased the pain.That was enough.
-Isabelle|Finish the Song|Even if I am gone,please sing this song to the end.
-Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove.Dive if you want it.
-Acolyte Roa|Confession of Doubt|My prayers were unanswered.Still,I will not stop praying.
-Fisherman Hald|The Last Catch|There was no catch today.But I spoke with the sea.
-Traveler Cyan|A Passing Point|This is not the end.It is only a passing point.
-Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm.End of report.
-Mother|To My Child|Put on your cloak when it gets cold.Promise me.
-Bard Fey|An Unfinished Poem|The rhyme is missing.To whoever finishes it.
-Mercenary Captain Volk|Order to Retreat|Come back alive.Honor can be picked up later.
-Little Girl|My First Journey|I'm a little scared.But it's fun.
-Someone|To Whoever Finds This|If you are reading this,the world is still going on.
+          <t>Lucia|The Ship That Never Returned|If this bottle reaches someone, I will likely be beneath the sea by then. But the sky was very blue.
+An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword. But I want someone to know I did not run.
+Ernes|Prayer of the Surf|God, if you cannot calm the waves, then at least grant me sleep.
+Mireille|The Promised Shore|If I arrive first, I will light a fire and wait. Come without losing your way.
+Navigator Daros|Record of the Stars|The stars were correct again today. The one who erred was me.
+Selena|A Small Confession|I could never speak your name aloud. That is my only regret.
+Old Man|To My Younger Days|The sea takes much, but nothing is entirely wasted.Survive.
+The Younger Twin|Half the World Left|Brother, half the world is still here. So please come back.
+Ship Doctor Renato|Medical Notes|I could not heal the wounds, but I eased the pain. That was enough.
+Isabelle|Finish the Song|Even if I am gone, please sing this song to the end.
+Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove. Dive if you want it.
+Acolyte Roa|Confession of Doubt|My prayers were unanswered. Still, I will not stop praying.
+Fisherman Hald|The Last Catch|There was no catch today. But I spoke with the sea.
+Traveler Cyan|A Passing Point|This is not the end. It is only a passing point.
+Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm. End of report.
+Mother|To My Child|Put on your cloak when it gets cold. Promise me.
+Bard Fey|An Unfinished Poem|The rhyme is missing. To whoever finishes it.
+Mercenary Captain Volk|Order to Retreat|Come back alive. Honor can be picked up later.
+Little Girl|My First Journey|I'm a little scared. But it's fun.
+Someone|To Whoever Finds This|If you are reading this, the world is still going on.
 Unknown|I...|I'm...going...home...!
-Unknown|I'm...|Moudamepo</t>
+Unknown|I'm...|Moudamepo
+Pirate King|My treasure?|Find it! I left everything in this world there!
+Pirate|Watch me|I’m gonna be King of the Pirates!!</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3358,12 @@
           <t>mysilia</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Humanos e Eleas vivem em paz em Mysilia._x000D_
-A Guerra dos Dez Anos feriu profundamente este país._x000D_
-Não se ouvem muitos bons rumores sobre o herdeiro do Lorde Jonan, o Lorde Efrond._x000D_
-Nosso país foi assolado por uma praga misteriosa após a Guerra dos Dez Anos. Há rumores de que a doença foi espalhada pelo vento milagroso de Nymelle._x000D_
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Humanos e Eleas vivem em paz em Mysilia.
+A Guerra dos Dez Anos machucou este país profundamente.
+Não ouvimos muitos bons rumores sobre o herdeiro do Lorde Jonan, o Lorde Efrond.
+Nosso país foi atingido por uma peste misteriosa depois da Guerra dos Dez Anos. Corre rumor de que a doença foi espalhada por aquele vento milagroso de Nymelle.
 O que será de Mysilia quando o império recuperar suas forças?</t>
         </is>
       </c>
@@ -3234,13 +3392,13 @@
           <t>olvina</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bem-vindo a Olvina, a vila do vinho, das fontes termais e das flores de cerejeira._x000D_
-Fico realmente impressionado com o entusiasmo de Theolucia por aprender._x000D_
-Mal posso esperar por outro concurso da túnica molhada!_x000D_
-Quero ser amaldiçoado pela Farris com toda a fúria dela._x000D_
-Olvina é a melhor vila turística de toda Mysilia.</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Bem-vindo a Olvina, a vila do vinho, das águas termais e das cerejeiras.
+Fico realmente impressionado com o entusiasmo de Theolucia pelo estudo.
+Mal posso esperar pelo próximo concurso de túnicas molhadas!
+Quero ser amaldiçoado pela Farris com todas as forças dela.
+Olvina é a melhor vila turística de Mysilia.</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -3268,10 +3426,10 @@
           <t>lothria</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>O Lorde Cetrus raramente sorri desde que a Lady Friaune faleceu._x000D_
-Todos agora chamam este forte de Willow, mas ele costumava ter outro nome.</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>O Lorde Cetrus quase não ri desde que a Dama Friaune faleceu.
+Todos hoje chamam este forte de Salgueiro, mas ele tinha outro nome.</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -3293,13 +3451,13 @@
           <t>derphy</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bem-vindo a Derphy, um ninho podre de escória e vilania._x000D_
-Muitos ladrões se reúnem aqui. Eles têm um esconderijo debaixo da taverna, mas não vão simplesmente deixar você entrar._x000D_
-A escravidão é um negócio extremamente lucrativo. Muitos dizem que é maligna, mas até mesmo a poderosa economia de Palmia ruiria se não houvesse escravos para trabalhar nos campos._x000D_
-Nada supera uma luta sangrenta na arena. Se quiser impressionar o público, entregue a eles drama e sangue._x000D_
-Derphy não tem guardas na cidade, então podemos fazer o que quisermos!</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Bem-vindo a Derphy, um favo podre de escória e vilania.
+Muitos ladrões circulam por aqui. Têm um esconderijo embaixo da taverna, mas não deixam você entrar assim.
+A escravidão é um negócio muito lucrativo. Muita gente jura que é mal, mas até a economia da poderosa Palmia desmoronaria se não tivessem escravos para lavrar os campos.
+Nada supera uma luta sangrenta na arena. Se quer impressionar a plateia, dê drama e sangue à vontade.
+Derphy não tem guardas municipais, então fazemos o que quisermos!</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -3327,14 +3485,14 @@
           <t>palmia</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Palmia é enorme. Eu vivia me perdendo por aqui. Às vezes é bem difícil encontrar outras pessoas._x000D_
-Bem-vindo à capital de Palmia! Nosso reino é antigo e muito próspero._x000D_
-O Príncipe Xabi e a Rainha Stasha formam um casal encantador._x000D_
-Um de nossos produtos especiais são brinquedos que a nobreza costuma comprar._x000D_
-Um amigo me contou sobre uma fortaleza antiga ao norte. Será que é verdade?_x000D_
-Temos muitas festas em Palmia. A nobreza joga dinheiro ao vento por qualquer desculpa para uma celebração regada a bebida.</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Palmia é enorme. Me perco nesta cidade o tempo todo. Às vezes é difícil achar outras pessoas.
+Bem-vindo à capital Palmia! Nosso reino é antigo e muito próspero.
+O príncipe Xabi e a rainha Stasha são um belo casal.
+Um dos nossos produtos especiais aqui são os brinquedos que a nobreza costuma comprar.
+Um amigo me contou que há uma fortaleza antiga ao norte. Será que é verdade?
+Temos muitas festas em Palmia. A nobreza joga dinheiro por qualquer desculpa de comemoração bêbada.</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -3362,16 +3520,16 @@
           <t>yowyn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Esta vila se chama Yowyn._x000D_
-Os cavalos vendidos aqui são os melhores de toda a região._x000D_
-Sempre nos faltam mãos durante a época da colheita. Tenho certeza que todos da vila ficariam felizes com sua ajuda._x000D_
-Às vezes vemos foras da lei conhecidos indo para o oeste após saquearem nossas fazendas ou matarem nosso gado. Será que tem algo por lá?_x000D_
-Saia da vila em direção leste e siga a estrada ao norte para chegar à capital do Reino de Palmia._x000D_
-O ancião vive falando de um castelo velho e caindo aos pedaços a sudoeste. Aquele velhote vive inventando histórias malucas._x000D_
-A economia de Yowyn é pequena, mas fazemos caixões de excelente qualidade. Às vezes, os nobres de Palmia mandam seus criados até aqui para comprá-los._x000D_
-O ar aqui no campo é tão puro e cheio de vida. Eu não trocaria isso por nada.</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Esta vila se chama Yowyn.
+Os cavalos vendidos aqui são os melhores da terra.
+Sempre faltam mãos na época da colheita. Tenho certeza de que todos na cidade ficariam felizes com sua ajuda.
+Às vezes vemos bandidos conhecidos indo para o oeste depois de assaltar nossas fazendas ou matar nosso gado. Será que tem algo por lá?
+Siga para o leste saindo da vila, e pegue a estrada para o norte até chegar à capital do Reino de Palmia.
+A anciã vive falando de um velho castelo caindo aos pedaços a sudoeste. Aquela velha bruxa vive inventando histórias malucas.
+A economia de Yowyn é bem pequena, mas fazemos caixões excelentes. Às vezes os nobres de Palmia mandam seus escudeiros e criados até aqui para comprá-los.
+O ar é tão fresco e vivo aqui no campo. Não trocaria isto por nada.</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -3403,14 +3561,14 @@
           <t>lumiest</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Lumiest é uma cidade de grande cultura e arte. Bem-vindo à nossa bela cidade._x000D_
-Ouvi dizer que há uma cidade famosa por suas fontes termais em algum lugar._x000D_
-Aqui em Lumiest, você pode pescar onde quiser._x000D_
-Eu poderia passar horas falando sobre pintura._x000D_
-É aqui que a guilda dos magos mantém suas bibliotecas. É o único lugar em todo o Norte de Tyris com uma guilda para magos._x000D_
-Dizem que algo horrível vive nos esgotos. O cheiro é terrível, então eu nunca desceria lá.</t>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Lumiest é uma cidade de grande cultura e arte. Bem-vindo à nossa bela cidade.
+Ouvi dizer que há uma vila famosa pelas águas termais em algum lugar.
+Aqui em Lumiest, você pesca onde quiser.
+Eu conseguiria falar de pintura por horas.
+Aqui é onde a guilda dos magos guarda suas bibliotecas. É o único lugar de toda Tyris do Norte que tem guilda para magos.
+Dizem que algo horrível vive nos esgotos. Mas o cheiro é terrível, então eu jamais desceria lá.</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -3440,13 +3598,13 @@
           <t>noyel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Está mais frio que o beiço da morte pendurado num poço. Mas, sabe... bem-vindo a Noyel._x000D_
-A neve nunca vai embora, mas ainda temos que limpá-la pra conseguir andar por aí._x000D_
-Você pode confessar seus pecados na igreja. Não consigo pensar em jeito melhor de ser perdoado pelos seus crimes._x000D_
-Estou congelando. Não consigo sentir meus dedos._x000D_
-Um tempo atrás vi uma casinha ao sul de Noyel. Parecia algum tipo de oficina.</t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>É mais frio que o pinto da morte pendurado num poço. Mas, sabe, bem-vindo a Noyel.
+A neve nunca vai embora, mas ainda temos de palear para poder circular.
+Você pode confessar seus pecados na igreja. Não consigo pensar num jeito melhor de ser perdoado pelos seus crimes.
+Estou congelando. Não sinto os dedos.
+Um tempo atrás vi uma casinha ao sul de Noyel. Parecia uma espécie de oficina.</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -3474,14 +3632,14 @@
           <t>kapul</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ah, não há nada como o cheiro salgado da brisa do mar._x000D_
-Adoro assistir às lutas brutais na arena de mascotes. Mas é bom tomar cuidado — às vezes o público leva bala perdida ou é atingido por dragões descuidados._x000D_
-Se quiser o melhor treinamento que um guerreiro pode ter, vá conhecer a guilda dos lutadores._x000D_
-O preço da carga de frutos do mar sobe muito mais para o interior._x000D_
-Fico curioso sobre como entrar naquela Pirâmide ao norte da cidade._x000D_
-Ouvi dizer que muita gente sinistra e estranha vai para Derphy.</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Ah, não existe nada como o cheiro salgado da brisa do mar.
+Adoro ver as lutas brutais da arena de bichos. Mas cuidado: às vezes gente da plateia leva bala perdida ou apanha de dragões distraídos.
+Se você quer o melhor treino que um lutador pode ter, conheça a guilda dos lutadores.
+O preço da carga de frutos do mar é bem alto mais para o interior.
+Como será que se entra naquela Pirâmide ao norte da cidade?
+Ouvi dizer que muita gente viscosa e sinistra vai parar em Derphy.</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -3512,17 +3670,17 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Produzimos muito mais arroz do que precisamos, então vendemos o excedente para os humanos.
-O Lorde Kizuami é a divindade patrona desta vila.
-O rio que atravessa esta vila nasce nas montanhas, perto de Larna.
-Nossos ancestrais cortaram terraços nestas colinas para cultivar arroz.
-É importante que todos na vila saibam escrever da forma tradicional.
-Se você se interessa por caligrafia, a loja geral vende os instrumentos.
-Se você vir qualquer fogo-fátuo dourado nos arrozais, avise a Kinu imediatamente. São espíritos malignos que tentam desviar os outros do caminho.
-Esta vila também cultiva muitos vegetais, como rabanetes e alho-poró.
-Kinu faz o cultivo de arroz parecer tão fácil.
-Apenas aqueles fiéis ao Lorde Kizuami conseguem perceber a energia espiritual da vila.
-Viajantes a caminho de Larna às vezes descansam na estalagem da vila antes de subir a trilha da montanha.</t>
+          <t>Produzimos muito mais arroz do que precisamos, então vendemos o excedente aos humanos.
+O Lorde Kizuami é a divindade padroeira desta vila.
+O rio que corta esta vila nasce nas montanhas, perto de Larna.
+Nossos ancestrais talharam terraços nestas encostas para plantar arroz.
+É importante que todos na vila saibam escrever do jeito tradicional.
+Se se interessa por caligrafia, o armazém vende as ferramentas.
+Se vir quaisquer fogos-fátuos dourados junto aos arrozais, avise a Kinu imediatamente. São espíritos malignos que te levam para o caminho errado.
+Esta vila também planta muitos legumes, como rabanetes e alho-poró.
+A Kinu faz o cultivo de arroz parecer tão fácil.
+Só os fiéis ao Lorde Kizuami conseguem perceber a energia espiritual da vila.
+Quem viaja para Larna às vezes descansa na estalagem da vila antes de subir o passo da montanha.</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -3564,20 +3722,20 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>É assustador sair da vila. Os humanos tocam nas nossas orelhas e rabos como bem entendem.
-Lady Horome cuida de todos nesta vila.
-Todos esses turistas estão estragando o clima da nossa vila.
-Dizem que se você ficar sozinho debaixo da cerejeira à noite, pode ver uma raposa dourada de nove caudas.
-Todo mundo nesta vila é treinado em esgrima desde pequeno.
+          <t>É assustador sair da vila. Os humanos tocam nossas orelhas e caudas como querem.
+A Dama Horome vigia todos nesta vila.
+Os turistas todos estão arruinando a atmosfera da nossa vila.
+Dizem que se você estiver sozinho junto à cerejeira à noite, pode ver uma raposa dourada de nove caudas.
+Todos nesta vila treinam esgrima desde pequenos.
 O leite vendido nesta vila é o melhor!
 Os mifu trazem arroz do sul até aqui para ser fermentado.
-O saquê de flor de cerejeira é uma oferenda apreciada pelos nossos dois deuses.
-A Mizuno tem um corpo bem forte, né? Pois é... grande e robusto.
-Entre o esforço da Misaki e da Mizuno, esta vila é segura e próspera.
-Apesar de estarmos tão ao norte, o ar nesta vila é quente e ameno. Até a árvore sagrada não perde as folhas no inverno.
+O saquê de flor de cerejeira é uma oferenda que agrada aos nossos dois deuses.
+A Mizuno tem um corpo bem robusto, não tem? Isso... grande e robusto.
+Entre o trabalho duro da Misaki e da Mizuno, esta vila é segura e próspera.
+Apesar de tão ao norte, o ar desta vila é quente e suave. Até a árvore sagrada não perde as folhas no inverno.
 O saquê de flor de cerejeira é a especialidade da nossa vila.
-Meditar debaixo da cachoeira purifica corpo e mente de influências malignas.
-Só aqueles que são fiéis à Lady Horome conseguem ver a verdadeira beleza da vila.</t>
+Meditar sob a cachoeira purifica corpo e mente das más influências.
+Só os fiéis à Dama Horome conseguem ver a verdadeira beleza da vila.</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -3625,17 +3783,17 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Estamos muito longe das estradas, então a maioria dos suprimentos chega pelo ar.
+          <t>Estamos muito longe das estradas, então a maioria das mercadorias chega por via aérea.
 Muitos aventureiros se reúnem em Specwing para formar grupos antes de se aventurar nas nefia.
-Specwing é a última parada para suprimentos de muitos grupos de aventureiros antes de entrarem na natureza remota de North Tyris.
-As nefia na região ao redor são mais perigosas do que o normal.
-Ouvi dizer que há uma Nefia peculiar aqui perto onde é preciso uma licença especial da Embaixada para explorá-la.
+Specwing é a última parada de suprimentos para muitos grupos antes de entrar no ermo remoto de Tyris do Norte.
+As Nefia da região ao redor são mais perigosas que o normal.
+Ouvi dizer que há uma Nefia peculiar por aqui onde você precisa de uma licença especial da Embaixada para explorar.
 Esta vila foi originalmente fundada por fadas.
 Tudo nesta vila foi ampliado quando os aventureiros começaram a visitar.
-A folia interminável no topo das árvores é como tiramos dinheiro dos aventureiros.
-Dizem que o fundador de Specwing era uma fada que se vestia com uma fantasia de berinjela azul.
-A magia das fadas permite que a árvore cresça e prospere mesmo com pessoas morando dentro dela.
-Nós cuidamos dela, e ela cuida da gente.</t>
+A farra interminável nas copas das árvores é como tiramos o dinheiro dos aventureiros.
+Dizem que a fundadora de Specwing era uma fada vestida de berinjela azul.
+A magia das fadas permite que a árvore cresça e prospere mesmo com gente morando nela.
+A gente cuida dela, e ela cuida da gente.</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -3677,22 +3835,22 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Uma #race nesta vila...?
-O que traz uma #race até esta vila?
+          <t>Um #race nesta vila...?
+O que traz um #race a esta vila?
 A barreira protege a vila de monstros e olhos curiosos.
 Às vezes, precisamos adquirir materiais de pesquisa do mundo exterior.
-Todos por quem me importei se foram há eras. Agora, ninguém no mundo lá fora se lembra de mim...
-Pelos nossos pecados contra os deuses, trabalhamos a serviço de nosso grande pai.
-O Ancião Bicerin não fala muito sobre a própria idade.
-Todos estão esperando que você traga comida que não tenha gosto de cinzas.
-Esta vila está com falta de ingredientes.
+Todos por quem me importei partiram há eras. Agora ninguém no mundo exterior se lembra de mim...
+Por nossos pecados contra os deuses, labutamos a serviço do nosso grande pai.
+O ancião Bicerin não fala muito da própria idade.
+Todos esperam que você traga comida que não tenha gosto de cinzas.
+Esta vila está sem ingredientes.
 Nenhum de nós morre de morte natural.
-Nossa libertação só virá quando nosso grande pai julgar que nossos pecados foram totalmente pagos.
-O conhecimento que preservamos é perigoso demais para se espalhar.
+Nossa libertação só virá quando nosso grande pai julgar nossos pecados pagos por completo.
+O conhecimento que curamos é perigoso demais para se espalhar.
 O olho do nosso grande pai está sempre sobre nós.
-Nosso grande pai supervisiona nossa penitência, e não há escapatória de nossos destinos.
-Com o tempo, nos preocupamos cada vez menos com nossas condições materiais...
-Sim, #race, você está diante de um exilado que vive há mais de mil anos.</t>
+Nosso grande pai supervisiona nossa penitência, e não há fuga de nossos destinos.
+Conforme o tempo passa, ficamos menos preocupados com nossas condições materiais...
+Sim #race, você está diante de um exilado que vive há mais de 1000 anos.</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -3749,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.58" customWidth="1" style="13" min="1" max="1"/>
@@ -3795,7 +3953,7 @@
           <t>mimu</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>…Pi?
 ……Pipi
@@ -3823,29 +3981,97 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="126.85" customHeight="1" s="14">
+    <row r="6" ht="53.7" customHeight="1" s="14">
       <c r="A6" s="13" t="inlineStr">
         <is>
+          <t>mamani</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Um dia, as máquinas reinarão sobre a terra no lugar da humanidade.
+Quanto tempo aquele altar do belicista está aqui?
+Parece que meu corpo velho ainda resta na superfície.
+Certamente você não acredita que os deuses são onipotentes?
+Você é livre para acreditar que o mundo tem um propósito, mas não espere demais da competência do designer dele.</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>機械はやがて人間の代わりに地上を支配するだろう。
+あの戦狂いの祭壇は、いつからここにあるんだ？
+生身だった頃の私の体が、まだ地上に残っているようだ。
+神が全能など、戯言だと思わないか？
+世界に目的があると信じるのは自由だが、設計者の技量には期待しないことだ。</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>One day, machines will rule the earth in place of humankind.
+How long has that warmonger's altar been here?
+It seems my old body still remains on the surface.
+Surely you do not believe that gods are omnipotent?
+You are free to believe that the world has a purpose, but do not expect too much from its designer's competence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="53.7" customHeight="1" s="14">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>mamani2</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Um dia, as máquinas reinarão sobre a terra no lugar da humanidade.
+Quanto tempo aquele altar do belicista está aqui?
+Parece que meu corpo velho ainda resta na superfície.
+Certamente você não acredita que os deuses são onipotentes?
+Você é livre para acreditar que o mundo tem um propósito, mas não espere demais da competência do designer dele.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>機械はやがて人間の代わりに地上を支配するだろう。
+あの戦狂いの祭壇は、いつからここにあるんだ？
+生身だった頃の私の体が、まだ地上に残っているようだ。
+神が全能など、戯言だと思わないか？
+世界に目的があると信じるのは自由だが、設計者の技量には期待しないことだ。</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>One day, machines will rule the earth in place of humankind.
+How long has that warmonger's altar been here?
+It seems my old body still remains on the surface.
+Surely you do not believe that gods are omnipotent?
+You are free to believe that the world has a purpose, but do not expect too much from its designer's competence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="126.85" customHeight="1" s="14">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
           <t>namamani</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>O que é este lugar?
-Deuses? Eles são apenas um pouco mais fortes e mais arrogantes que os humanos.
-O comportamento humano é sempre guiado pela falha da emoção.
-Quando uma máquina quebra, é culpa do seu design, não é?
-Um dia, as máquinas governarão a terra no lugar da humanidade.
-Eu lembro de tudo que criei—sem exceção.
-Eu me recuso a reconhecer algo tão irracional quanto um deus.
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Que lugar é este?
+Deuses? São só um pouco mais fortes e arrogantes que humanos.
+O comportamento humano é sempre guiado pelo mau funcionamento da emoção.
+Quando uma máquina quebra, a culpa é do design dela, não é?
+Um dia, as máquinas reinarão sobre a terra no lugar da humanidade.
+Lembro de tudo o que criei: sem exceção.
+Me recuso a reconhecer algo tão irracional quanto um deus.
 Por que há dois de mim aqui?
-Que lugar entediante. Exceto, é claro, pelo fato de que há dois de mim.
+Que lugar monótono. Exceto, claro, pelo fato de que há dois de mim.
 ...Este braço? Claro que eu mesmo o substituí.
-Você acha que estou atrás do trono dos deuses? Heh, que pensamento engraçado. Prefiro muito mais abrir sua cabeça e ver como funciona.
-...Por que há tantos gatos aqui?</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+Acha que estou atrás do trono dos deuses? Heh, que pensamento engraçado. Eu preferiria desmontar sua cabeça e ver como funciona.
+...Por que tem tantos gatos aqui?</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>なんだこの場所は？
 神々なんて、ただ人間より少し強くて傲慢なだけじゃないか。
@@ -3861,7 +4087,7 @@
 …やけに猫が多いな。</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>What is this place?
 Gods? They're just a little stronger and more arrogant than humans.
@@ -3878,51 +4104,51 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="12.8" customHeight="1" s="14">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="9" ht="12.8" customHeight="1" s="14">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>namamani2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Estranho... Não consigo me lembrar de nada.</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Estranho... Não consigo lembrar de nada.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>おかしい、何も思い出せない。</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Strange... I can't remember anything.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="126.85" customHeight="1" s="14">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="10" ht="126.85" customHeight="1" s="14">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>keeper_garden</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tanelorn? Ah, já ouvi alguém chamar este lugar por esse nome antes.
-O que foi? Você também deseja ser mimado por mim?
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Tanelorn? Ah, já ouvi alguém chamar este lugar por esse nome.
+Que foi? Quer também ser mimado por mim?
 O tempo não tem significado aqui.
-Oh? Um viajante, um perdido, ou talvez apenas um tolo vagando sem saber aonde veio?
-Muwohoho... quão cortês de sua parte me cumprimentar, mortal.
-Gatos realmente são os melhores, não são?
-No fim, todo convidado parte—esquecendo este jardim, e retornando para onde, e quando, eles pertenceram.
+Oh? Um viajante, um perdido, ou talvez só um tolo vagando sem saber de onde veio?
+Muwohoho... que cortesia a sua em me cumprimentar, mortal.
+Gatos são verdadeiramente os melhores, não são?
+No fim, todo hóspede parte: esquece este jardim e volta para onde, e quando, pertencia.
 Aqui neste jardim, todas as almas conhecem a paz.
-Todos que vagam por aqui partem com um fragmento de sua calma eterna.
-Aqui, corações flutuam como pétalas sobre águas calmas, intocados pelo tempo.
-Este jardim se lembra de toda alma que já encontrou descanso dentro de seu silêncio.
-Um dia, vou afofar a Deusa da Fortuna até me satisfazer.</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+Todos os que vagam por aqui partem com um fragmento de sua calma eterna.
+Aqui, os corações flutuam como pétalas sobre água parada, intocados pelo tempo.
+Este jardim lembra cada alma que já encontrou repouso em seu silêncio.
+Um dia, farei carinho na Deusa da Sorte à vontade.</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>タネローン？ ああ、誰かが庭をそう呼ぶのを聞いたことがあるな。
 なんじゃ、ぬしもわっちに可愛がられたい口か？ 
@@ -3938,7 +4164,7 @@
 いつか、幸運の女神を思う存分モフりたいものじゃ。</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Tanelorn? Ah, I’ve heard someone call this place by that name before.
 What is it? Do you wish to be doted on by me as well?
@@ -3955,27 +4181,27 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="105.95" customHeight="1" s="14">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="11" ht="105.95" customHeight="1" s="14">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>erishe</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Hehe, irmão, para onde você foi?
-Olá, viajante. Por favor, tome seu tempo e descanse aqui.
-Este é um lugar tão pacífico. Estar aqui quase faz você esquecer do próprio tempo...
-Eu me separei do meu irmão no caminho para a peça. O que será que aconteceu?
-Nenhum de nós está realmente interessado em teatro, mas em Zanan, é considerado parte da educação de um nobre.
-Você sabia? ...Há fadas em Altheheit, sabe.
-Mesmo não parecendo, meu irmão é inútil sem mim, hehe.
-Loyter uma vez jogou uma pedra em uma sala de concertos e foi banido de entrar.
-Sempre que trago um presentinho para Loyter, ele ainda cora como um menino.
-Loytel...? Acho que não, embora eu conheça Loyter.</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+Olá, viajante. Por favor, fique à vontade e descanse aqui.
+Este lugar é tão pacífico. Estar aqui quase faz você esquecer o próprio tempo...
+Me separei do meu irmão a caminho da peça. O que teria acontecido?
+Nenhum de nós é muito fã de teatro, mas em Zanan isso é considerado parte da educação de um nobre.
+Sabia? ...Há fadas em Altheheit, sabia?
+Mesmo que não pareça, meu irmão é um caso perdido sem mim, hehe.
+Loyter certa vez jogou uma pedra numa sala de concertos e acabou banido de entrar.
+Toda vez que levo um presentinho ao Loyter, ele ainda fica vermelho como um menino.
+Loytel...? Acho que não, mas eu conheço o Loyter.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>ふふ、兄さん、どこにいったの？
 こんにちは、旅の人。ゆっくりしていってください。
@@ -3989,7 +4215,7 @@
 ロイテル…？ いえ、ロイターさんなら知ってますけど…</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Hehe, brother, where did you go?
 Hello, traveler. Please, take your time and rest here.
@@ -4004,26 +4230,26 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="105.95" customHeight="1" s="14">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="12" ht="105.95" customHeight="1" s="14">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>larnneire</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Oh, você conhece o conto de fadas do príncipe que foi transformado em uma besta horrível?
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Oh, você conhece o conto de fadas do príncipe que virou uma fera feia?
 Somos mensageiros de Vindale.
-Nossa jornada termina aqui em North Tyris na grande cidade de Palmia onde devemos ter uma conversa com o Rei Xabi, um homem de justiça e compaixão.
-North Tyris é um continente no hemisfério ocidental de Ylva.
+Nossa jornada termina aqui em Tyris do Norte, na grande cidade de Palmia, onde devemos conversar com o rei Xabi, um homem de justiça e compaixão.
+Tyris do Norte é um continente no hemisfério ocidental de Ylva.
 Que o Vento esteja sempre com você.
-...Onde nós viemos parar?
-Mysilia? Sim, eu conheço. Mas Mysilia é...
-Humanos... eles me assustam, mas possuem tanto fascínio.
-A maioria dos desejos que habitam nos corações humanos estão ausentes em nós Elea. Não temos interesse em possuir, em governar, ou em lutar. Mas se isso é melhor é outra questão.</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+...Onde viemos parar?
+Mysilia? Sim, conheço. Mas Mysilia é...
+Humanos... eles me assustam, mas têm tanto encanto.
+A maioria das cobiças que moram nos corações humanos não existe em nós, Elea. Não temos interesse em possuir, em reinar ou em lutar. Mas se isso é para o melhor, é outra história.</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>あら、獣に変えられた王子の童話を、あなたは知っているの？
 私達はヴィンデールの森からの使者。
@@ -4036,7 +4262,7 @@
 人間の抱く欲求の多くを、エレアは持たない。私たちは所有することにも、支配や戦うことにも興味がないの。それが良いことかは別としてね。</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Oh, you know the fairy tale of the prince who was turned into an ugly beast?
 We are messengers from Vindale.
@@ -4050,28 +4276,28 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="116.4" customHeight="1" s="14">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="13" ht="116.4" customHeight="1" s="14">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>lomias</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Parece que você não está familiarizado com esta terra.
-O que você verá neste mundo, e que pegadas você deixará para trás?
-Hah, vagamos para um lugar estranho.
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Parece que você não conhece esta terra.
+O que você verá neste mundo, e que pegadas deixará?
+Hah, vagamos até um lugar estranho.
 Estamos a caminho de Palmia.
-Do que você está falando? É o ano 517 de Sierra Terre. é claro.
-Desbravar Vernis? Você bateu a cabeça?
-Que coincidência. acabamos de terminar de cuidar de um aventureiro que se parecia muito com você.
-Honestamente, nossa jornada urgente foi atrasada tudo por causa de um aventureiro caído.
-...Pare com seus olhos curiosos. Sim, somos parentes da Floresta. A floresta que vocês ridicularizam como "Outro".
-Uma vez que um Elea deixa a Floresta, a Floresta nunca mais os receberá novamente. Naturalmente, Larnneire e eu ficamos separados, pois é o papel do enviado tratar com humanos.
-Larnneire herda uma linhagem diferente de qualquer outra entre os Elea. Mas é melhor eu não dizer mais nada, para que ela não me lembre severamente de novo!</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+Do que está falando? É o ano 517 de Sierra Terre, claro.
+Pioneirar Vernis? Bateu a cabeça?
+Que coincidência. acabamos de atender um aventureiro que parecia muito com você.
+Sinceramente, nossa jornada urgente foi atrasada por causa de um aventureiro desmaiado.
+...Cesse seus olhos curiosos. Sim, somos parentes da Floresta. A floresta que vocês depreciam como "Outra".
+Quando um Elea deixa a Floresta, a Floresta nunca mais o recebe. Naturalmente, Larnneire e eu estamos à parte, pois é papel do enviado negociar com os humanos.
+Larnneire herda uma linhagem única entre os Elea. Mas é melhor eu não dizer mais nada, para ela não me repreender de novo com rigor!</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>見たところ君はノースティリスの人間ではないようだ。
 君はこの世界で何を見て、如何な足跡を残すのかな？
@@ -4086,7 +4312,7 @@
 ラーネイレはエレアの中でも特別な血筋を受け継いでいる。おっと、彼女に口酸っぱく言われる前にこの話は止めておこう！</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>It looks like you aren't familiar with this land.
 What will you see in this world, and what footprints will you leave behind?
@@ -4102,21 +4328,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="43.25" customHeight="1" s="14">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="14" ht="43.25" customHeight="1" s="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>conery</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Queria que meu príncipe tivesse um pouco mais de moderação como herdeiro de Palmia._x000D_
-São pessoas como Gilbert que fazem meu príncipe parecer mal._x000D_
-Como é cortês e decidida a Princesa Stasha para a sua idade! Ela é verdadeiramente um ídolo da corte real!_x000D_
-Vida longa à Princesa Stasha!</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Queria que meu príncipe tivesse um pouco mais de moderação como herdeiro de Palmia.
+É gente como Gilbert que faz meu príncipe ficar com fama ruim.
+Que cortesia e determinação a Princesa Stasha demonstra para a idade dela! Ela é de verdade um ídolo da corte real!
+Longa vida à Princesa Stasha!</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>若様には、パルミアの世継ぎとして、もう少し節操を持って頂きたいものだ。
 ギルバートのような輩がいるから、若様も悪ノリしてしまう。
@@ -4124,7 +4350,7 @@
 スターシャ姫万歳！</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>I wish my prince would have a little more moderation as the heir to Palmia.
 It is people like Gilbert who make my prince look bad.
@@ -4133,27 +4359,27 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32.8" customHeight="1" s="14">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="15" ht="32.8" customHeight="1" s="14">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>garokk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Meu parceiro Miral e eu nos conhecemos desde que éramos crianças que mal sabiam segurar um martelo._x000D_
-Sempre admirei o talento do Miral. E, mesmo assim, lá está ele, fazendo brinquedos de gato enquanto negligencia os pedidos dos clientes._x000D_
-Tédio. Preciso de uma grande encomenda para incendiar meu coração de artesão!</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Meu parceiro Miral e eu nos conhecemos desde crianças que não sabiam nem segurar um martelo.
+Sempre admirei o talento do Miral. E olha ele agora, fazendo brinquedos de gato enquanto negligencia os pedidos dos clientes.
+Que tédio. Preciso de uma encomenda grande para inflamar meu coração de artesão em brasa!</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>相棒のミラルとはまだ槌も持てぬガキの頃からの腐れ縁じゃ。
 ミラルの才能にはわしも一目置いておる。それなのにヤツときたら注文を放ったらかして猫の玩具など作っている情けない始末じゃよ。
 つまらんのう。わしのくすぶった職人のハートを燃え上がらせる大きな依頼はないものか！</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>My partner Miral and I have been known each other since we were kids who couldn't even hold a hammer.
 I have always admired Miral's talent. And yet, here he is, making cat toys while neglecting to fulfill customers' orders.
@@ -4161,23 +4387,23 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="64.15000000000001" customHeight="1" s="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="16" ht="64.15000000000001" customHeight="1" s="14">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>gilbert</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Muwahahaha! ...O que é você?_x000D_
-Pelo Opatos, vou esmagar cada inseto maligno que chegar perto da Princesa Stasha! Muwahaha!_x000D_
-Vida longa à Princesa Stasha!_x000D_
-Queria ter lutado na guerra há 15 anos!_x000D_
-Muwaha!_x000D_
-Ajudar os indefesos, esmagar a vilania!</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Muwahahaha! ...Que?
+Pelo Opatos, esmagarei cada inseto maligno que se aproximar da Princesa Stasha! Muwahaha!
+Longa vida à Princesa Stasha!
+Queria ter estado na guerra há 15 anos!
+Muwaha!
+Ajudar os desamparados, esmagar a vileza!</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>フハハハハ！…何だ貴様は？
 オパートスの名にかけて、スターシャ姫に近づく悪い虫は俺が全部退治してやる、フハハハハぁ！
@@ -4187,9 +4413,9 @@
 弱きを助け、悪を砕くのだ！</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>Muwahahaha! ...What are you?
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Muwahahaha! ...What?
 By Opatos, I'll squash every bad bug that gets near Princess Stasha! Muwahaha!
 Long live Princess Stasha!
 I wish I was in the war 15 years ago!
@@ -4198,46 +4424,46 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22.35" customHeight="1" s="14">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="17" ht="22.35" customHeight="1" s="14">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>jonan</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Que negócios você tem na corte de Mysilia?_x000D_
-Sou velho, mas ainda não posso me esconder.</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Que negócio você tem na corte de Mysilia?
+Estou velho, mas ainda não posso me esconder.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>ミシリア宮廷に何の用かな？
 私ももう年だ。だが、今はまだ隠居するわけにはいかない。</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>What business do you have at the court of Mysilia?
 I am old but I can't go into hiding just yet.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="43.25" customHeight="1" s="14">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18" ht="43.25" customHeight="1" s="14">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>lowell</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>O que um aventureiro está fazendo aqui, hein?_x000D_
-O asilo abriga e educa crianças sem pais._x000D_
-Mesmo nesses tempos, espero que nossas crianças cresçam saudáveis e felizes._x000D_
-Educação é importante. Essas crianças, que não têm nada atrás de si, eventualmente terão que encontrar um lugar onde trabalhar.</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>O que um aventureiro está fazendo aqui, hein?
+O asilo abriga e educa crianças que não têm pais.
+Mesmo nestes tempos, espero que nossas crianças cresçam saudáveis e felizes.
+Educação é importante. Estas crianças, que não têm nada atrás de si, um dia terão de achar um lugar para trabalhar.</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>冒険者がこんなところに何のようだね？
 アシュラムでは、親のいない子どもを養護し、教育している。
@@ -4245,7 +4471,7 @@
 教育は重要だ。何の後ろ盾もないこの子たちも、やがては働き口を見つけなければならない。</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>What's an adventurer doing here, eh?
 The asylum shelters and educates children who have no parents.
@@ -4254,27 +4480,27 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32.8" customHeight="1" s="14">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="19" ht="32.8" customHeight="1" s="14">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>mapMerchant</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Meu nome é Slan, servo de Palmia. Estou passando meu tempo viajando pelo mundo para aprimorar minhas habilidades._x000D_
-Estes são, de fato, livros valiosos._x000D_
-Cheguei a este castelo isolado num dia de neve e tenho ficado aqui há um tempo.</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Meu nome é Slan, um servo de Palmia. Atualmente passo meu tempo viajando pelo mundo para aperfeiçoar minhas habilidades.
+Estes são, de fato, livros valiosos.
+Cheguei a este castelo isolado num dia de neve e estou morando aqui há um tempo.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>私の名はスラン。パルミアに仕える身だ。今は研さんを積むために各地を放浪している。
 それにしても貴重な書物の数々だ。
 吹雪の日にこの孤城に辿り着いて、しばらく世話になっている。</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>My name is Slan, a servant of Palmia. I'm currently spending my time traveling around the world to improve my skills.
 These are indeed valuable books.
@@ -4282,27 +4508,27 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="43.25" customHeight="1" s="14">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="20" ht="43.25" customHeight="1" s="14">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>miral</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Oh, um visitante! Não hesite em brincar com meus gatos._x000D_
-Meu parceiro e eu costumávamos discutir sobre o nome da oficina. Se ele tivesse algum senso para nomes, não teria sugerido algo tão ridículo como "Garokk Miral"._x000D_
-O que vamos preparar para a refeição de hoje? Ultimamente, tenho me divertido mais pensando no cardápio dos gatos do que forjando ferro.</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Oh, uma visita! Fique à vontade para brincar com meus gatos.
+Meu parceiro e eu vivíamos discutindo o nome da oficina. Se ele tivesse o menor senso de nomenclatura, não teria inventado um nome tão ridículo quanto "Garokk Miral".
+O que faremos para a refeição de hoje? Ultimamente me divirto mais pensando no cardápio das refeições dos gatos do que na ferraria.</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>おお、客人か！なに、遠慮することはない、わしの猫たちと存分に戯れていってくれ。
 相棒とは工房の屋号でもめたものよ。奴に少しでもネーミングセンスというものがあれば、「ガロクミラル」などとふざけた名前を思いつくこともなかったじゃろうに。
 今日のご飯はなんにしようかぬ。最近は猫の食事の献立を考えるのが鍛冶よりも楽しくてな。</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Oh, a guest! Don't hesitate to play with my cats.
 My partner and I used to argue about the name of the workshop. If he had any sense of naming, he wouldn't have come up with such a ridiculous name as "Garokk Miral".
@@ -4310,21 +4536,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="53.7" customHeight="1" s="14">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="21" ht="53.7" customHeight="1" s="14">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>nino</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A vida de mercador é tranquila e despreocupada, mas não seria ruim me estabelecer numa cidade confortável em algum lugar. Sim, em Kapoor ou por aí._x000D_
-É raro ver um mercador homem-besta? Talvez você não veja muitos de nós em Tyris._x000D_
-Nos orgulhamos dos muitos itens que reunimos de Verizzia, a terra dos oceanos a oeste, até Nieca, a terra dourada do deserto a leste. Sinta-se à vontade para olhar._x000D_
-Não... isto não é uma fantasia.</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>A vida de mercador é boa e sem preocupações, mas não seria mal assentar numa cidade confortável em algum lugar. Sim, em Kapul ou por perto.
+É raro ver um mercador bestial? Talvez você não veja muitos de nós em Tyris.
+Temos orgulho dos muitos itens que juntamos de Verizzia, a terra dos oceanos a oeste, a Nieca, a terra dourada do deserto a leste. Fique à vontade e olhe à vontade.
+Não...não é fantasia.</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>隊商の暮らしも気ままでいいが、どこか住心地の良い街に腰を据えるのも悪くはないな。そう、カプールあたりに。
 獣人の商人は珍しいか？ティリスではあまり見かけないかもしれないな。
@@ -4332,52 +4558,52 @@
 いや…これはかぶりものではない。</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>The life of a merchant is nice and carefree, but it wouldn't be bad to settle down in a comfortable town somewhere. Yes, in Kapoor or thereabouts.
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>The life of a merchant is nice and carefree, but it wouldn't be bad to settle down in a comfortable town somewhere. Yes, in Kapul or thereabouts.
 Is it rare to find a beastman merchant? Perhaps you don't see many of us in Tyris.
 We are proud of the many items we have gathered from Verizzia, the land of the oceans in the west, to Nieca, the golden land of the desert in the east. Take your time and look around.
 No...it's not a costume.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="12.8" customHeight="1" s="14">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="22" ht="12.8" customHeight="1" s="14">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>nola</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sou Nola, prefeita interina. Como posso ajudá-lo?</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Sou Nola, prefeita interina. Como posso ajudar?</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>市長代理のノーラです。何かご用ですか？</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>I am Nola, Acting Mayor. How may I help you?</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="43.25" customHeight="1" s="14">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="23" ht="43.25" customHeight="1" s="14">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>stasha</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Oh, como posso ajudar?_x000D_
-Palmia é um reino com grande história em Tyris. Estou honrada por ter sido recebida neste palácio real._x000D_
-Ídolo...? ...É uma língua estrangeira?_x000D_
-Os fãs... ah... a... as pessoas do Palácio Real têm sido muito gentis comigo.</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Oh, como posso ajudar?
+Palmia é um reino de grande história em Tyris. Estou honrada por ser recebida neste palácio real.
+Ídolo...? ...É uma língua estrangeira?
+Os fãs...ah...a...as pessoas do Palácio Real têm sido muito gentis comigo.</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>あら、私に何かご用ですか？
 パルミアは歴史あるティリスの大国。この王宮に迎えられて光栄です。
@@ -4385,7 +4611,7 @@
 王宮ではファン…あ…み…みなさんにとても良くしていただいています。</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Oh, how may I help you?
 Palmia is a kingdom with great history in Tyris. I am honored to be welcomed into this royal palace.
@@ -4394,27 +4620,27 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="32.8" customHeight="1" s="14">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="24" ht="32.8" customHeight="1" s="14">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>theolucia</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tenho interesse por história e folclore._x000D_
-Minha irmã Farris é muito assustadora quando fica brava._x000D_
-A Biblioteca Real de Palmia é um lugar maravilhoso com uma coleção enorme de livros.</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Me interesso por história e folclore.
+Minha irmã Farris é bem assustadora quando fica com raiva.
+A Biblioteca Real de Palmia é um lugar muito agradável, com uma coleção enorme de livros.</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>私は歴史と伝承に興味があります。
 ファリス姉さんは、怒らせると怖いですよ。
 パルミアの王宮図書館にはたくさんの蔵書があって、本当に素敵な所です。</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>I am interested in history and folklore.
 My sister Farris is very scary when she gets angry.
@@ -4422,27 +4648,27 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="32.8" customHeight="1" s="14">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="25" ht="32.8" customHeight="1" s="14">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>xabi</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Você é um aventureiro? Adoraria ouvir suas histórias._x000D_
-Meu pai é muito rígido. Odeio quando ele implica com tudo. Espero que Conery não seja mal influenciado por ele._x000D_
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Você é aventureiro? Adoraria ouvir suas histórias.
+Meu pai é rígido demais. Odeio quando ele mete o bedelho em tudo. Espero que o Conery não sofra má influência dele.
 Gilbert e Conery são meus amigos desde a infância.</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>君は冒険者か？ぜひ色々と話を聞かせてもらいたいものだ。
 父上は厳しすぎるのだ。何事にもいちいち小言を言われて嫌になるよ。コネリーが悪い影響を受けないといいが…
 ギルバートとコネリーは幼い頃からの友だ。主従関係はあっても、それは変わらないよ。</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Are you an adventurer? I'd love to hear your stories.
 My father is too strict. I hate it when he nitpicks at everything. I hope Conery doesn't get a bad influence from him.
@@ -4450,27 +4676,27 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="32.8" customHeight="1" s="14">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="26" ht="32.8" customHeight="1" s="14">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>zane</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>O que é você?_x000D_
-Este não é lugar para aventureiros. Deve partir agora._x000D_
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>O que é você?
+Este não é lugar para aventureiros. Vá embora agora.
 …</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>何だね、君は？
 ここは冒険者風情が訪れていい場所ではない。立ち去りたまえ。
 …</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>What are you?
 This is not a place for adventurers. You shall leave now.
@@ -4478,27 +4704,27 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="44.75" customHeight="1" s="14">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="27" ht="44.75" customHeight="1" s="14">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>ephrond</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Quem é você? Vá embora._x000D_
-Ah, que dia adorável e pacífico em Mysilia. Todas as pessoas aqui devem ter fechado os olhos ou os deixado em algum lugar._x000D_
-São todos um bando de tolos, alinhando seus rostos tolos.</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Quem é você? Vá embora.
+Ah, que dia encantador e pacífico em Mysilia. Todo o povo aqui deve ter fechado os olhos ou deixado em algum lugar.
+São todos um bando de tolos, enfileirando suas carinhas tolas.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>何だ貴様は？気安く話しかけるな。
 ああ、いとも愛らしく安穏としたミシリアの都の一日だ。ミシリアの民は皆、目を塞いでいるかどこかに置き忘れてしまったのだろう。
 呑気な顔を並べて、アホウ共が。</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Who are you? Go away.
 Ah, what a lovely and peaceful day in Mysilia. All the people here must have closed their eyes or left them somewhere.
@@ -4506,27 +4732,27 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="32.8" customHeight="1" s="14">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="28" ht="32.8" customHeight="1" s="14">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>eluminaire</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Por favor, fique longe... Lorde Efrond ficará bravo comigo._x000D_
-A Floresta de Vindale... nunca a visitei. Todos os elea que vivem em Mysilia são "forasteiros"._x000D_
-Olhar para as flores assim me dá sono...</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Fique longe, por favor... o Lorde Efrond ficará bravo comigo.
+A Floresta de Vindale... nunca a visitei. Todos os elea que vivem em Mysilia são "de fora".
+Olhar as flores assim me dá sono...</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>近づかないでください…エフロンド様に怒られます。
 異形の森？…私は訪れたことはありません。ミシリアに住むエレアは皆、「森の外」のエレアなのです。
 こうして花を眺めていると眠くなりますね…</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Please stay away...Lord Efrond will be angry with me.
 The Forest of Vindale...I have never visited it. All the elea who live in Mysilia are "outsiders".
@@ -4534,22 +4760,22 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56.7" customHeight="1" s="14">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="29" ht="56.7" customHeight="1" s="14">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>barrich</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Você ouvirá minha canção?_x000D_
-Servi na corte real de Zanan há muito tempo, mas, bem, cometi um erro._x000D_
-Mysilia é verdadeiramente meu lar agora._x000D_
-Você viu Melvin? Estou com vontade de cantar um pouco._x000D_
-Minha esposa é a mulher mais bela e brilhante de toda Mysilia. Ela é quase boa demais pra mim.</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Vai ouvir minha canção?
+Servi na corte real de Zanan há muito tempo, mas, bem, atrapalhei tudo.
+Mysilia agora é de verdade meu lar.
+Viu o Melvin por aí? Estou com vontade de cantar um pouco.
+Minha esposa é a mulher mais bela e brilhante de toda Mysilia. Ela é quase boa demais para mim.</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>一曲聴いてくかい？
 昔はザナンの王宮に仕えていたんだが、まあ、ヘマをやっちまってな…
@@ -4558,7 +4784,7 @@
 俺の妻はミシリアで一番美しく聡明だ。俺にはもったいないぐらいだよ。</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Will you listen to my song?
 I served in the royal court of Zanan long ago, but, well, I screwed up.
@@ -4568,22 +4794,22 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="79.09999999999999" customHeight="1" s="14">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="30" ht="79.09999999999999" customHeight="1" s="14">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>melvin</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Já se passaram oito anos desde que minha irmã se casou com Barrich. O tempo voa._x000D_
-Minha família carrega o título de Protetores da Floresta há gerações. Neste tempo difícil para os Elea, gostaria de provar que este título não é só um nome. Claro, seria melhor se tal oportunidade nunca surgisse._x000D_
-Meu parceiro, Griffin, é uma coruja selvagem. Cuidei dele quando estava ferido e ele se apegou a mim. Agora acha que meu ombro é a casa dele._x000D_
-A falta de moderação das damas é preocupante._x000D_
-Eluminaire, a moça que acompanha o Lorde Efrond, será que ela é... não, estou pensando demais.</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Já faz oito anos que minha irmã casou com Barrich. Como o tempo voa.
+Minha família detém o título de Protetor da Floresta há gerações. Neste tempo de provação para os Elea, gostaria de provar que este título não é só um nome. Claro, o melhor seria que tal oportunidade nunca se apresentasse.
+Meu companheiro, Griffin, é uma coruja selvagem. Cuidei dele quando estava ferido e ele se apegou a mim. Agora acha que meu ombro é a hospedagem dele.
+A falta de moderação das damas é preocupante.
+Eluminaire, a garota que acompanha o Lorde Efrond, será que ela é... não, estou pensando demais.</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>妹がベーリッヒの元に嫁いでもう八年が経つ。時が流れるのは早いものだ。
 私の家は、森の民の守護者の役職を代々受け継いできた。エレア達にとって苦難の時代の今、この称号が名ばかりでないことを証明したいよ。もちろん、そんな機会が訪れないのが一番だが。
@@ -4592,7 +4818,7 @@
 エフロンド様にお付きのエルミナレという娘、あの娘はまさか…いや、私の考え過ぎか。</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>It has already been eight years since my sister married Barrich. Time flies.
 My family has held the title of Protector of the Forest for generations. In this time of hardship for the Eleas, I would like to prove that this title is not just a name. Of course, it would be best if such an opportunity never presents itself.
@@ -4602,21 +4828,21 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="44.75" customHeight="1" s="14">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="31" ht="44.75" customHeight="1" s="14">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>caldorn</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>O que é você?_x000D_
-Aventureiro pode parecer algo legal, mas no fundo, não passa de um vagante sem vontade de trabalhar honestamente._x000D_
-Obviamente o império é uma ameaça. Mas Zanan, que esconde bem suas verdadeiras intenções, também me dá arrepios._x000D_
-O Rei Zane de Palmia é um monarca renomado, mas ouvi dizer que seu filho, o Príncipe Xabi, é um mimado. Parece que todo país tem o mesmo problema com seus herdeiros!</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>O que é você?
+Aventureiro pode soar bonito, mas no fundo são só andarilhos sem vontade de trabalhar honestamente.
+Óbvio que o império é uma ameaça. mas Zanan, que esconde as intenções reais com cuidado, também me arrepia.
+O rei Zane de Palmia é um monarca renomado, mas ouvi que o filho dele, o príncipe Xabi, é um mimado. Parece que todo país tem o mesmo problema com o herdeiro!</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>何だお主は？
 冒険者とは聞こえがいいが、要はまっとうに働く意志のない流れものではないか？
@@ -4624,7 +4850,7 @@
 パルミアのゼイン王は名君と名高いが、息子のジャビ王子は道楽者だと聞く。世継ぎに頭を悩まされるのはどの国も同じだな！</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>What are you?
 An adventurer may sound nice, but in essence, they are just a drifter without the will to work honestly.
@@ -4633,45 +4859,54 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="13.8" customHeight="1" s="14">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="32" ht="13.8" customHeight="1" s="14">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>melilith</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Qual é mais assustador, irmãs mais novas ou cubos? Pessoalmente, acho irmãs mais novas mais adoráveis.</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>O que assusta mais, irmãzinhas ou cubos? Pessoalmente, acho as irmãzinhas mais adoráveis, embora.</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>妹たちとキューブ、どちらが怖い？私は妹たちの方が可愛いと思ってるけど</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Which is scarier, younger sisters or cubes? I personally find younger sisters to be more adorable, though.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="179.1" customHeight="1" s="14">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="33" ht="179.1" customHeight="1" s="14">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>seeker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ah, um corvo. Busca algo?_x000D_
-Gostaria de um pouco de chá, corvo?_x000D_
-Eu sou o "Buscador"... ou pode me chamar de "Errante dos Reinos". Dediquei minha vida a adquirir todo o conhecimento deste mundo. Como pode ver, sou um recluso._x000D_
-É realmente notável que tenha encontrado um lugar tão remoto._x000D_
-...Este castelo é minha grande biblioteca, mas, fundamentalmente, uma biblioteca deve ser um lugar aberto a todos._x000D_
-Todo o conhecimento deste mundo deve ser acessível a todos. Sinta-se em casa.</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Ah, um corvo. Busca alguma coisa?
+Aceita um chá, corvo?
+ Eu sou o "Buscador"... ou pode me chamar de "Vagante dos Reinos". Dediquei minha vida a adquirir todo o conhecimento deste mundo. Como vê, sou um recluso.
+É bem notável que você tenha encontrado um lugar tão remoto.
+...Este castelo é minha grande biblioteca, mas, no fundo, uma biblioteca deveria ser um lugar aberto a todos.
+Todo o conhecimento deste mundo deveria ser acessível a todos. Sinta-se em casa.
+A Liga Eterna...? Você conhece um conto bem antigo, vejo.
+Ah, corvo. Está cuidando bem dos livros que pegou emprestado?
+Passar conhecimento às gerações futuras é o dever de quem o possui.
+Olá de novo, corvo. Não viu meu amigo Slan, viu?
+Este elmo? Uma bela fera, não é? É um velho amigo meu.
+Por que escondo meu rosto? Desde a Guerra dos Dez Anos, está difícil para um Elea andar livremente...
+Todos os meus amigos... partiram todos à minha frente.
+Aparentemente, há um louco perseguindo visões de uma certa "Pedreira da Irmã Cachorra Mais Nova".
+Será... haverá outra guerra?</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>やあ、ワタリガラス。なにか用かな。
 お茶でも飲むかい、ワタリガラス。
@@ -4691,7 +4926,7 @@
 また戦争が起こるのかな。</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Ah, a raven. Do you seek something?
 Would you like some tea, raven?
@@ -4711,69 +4946,69 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="12.8" customHeight="1" s="14">
-      <c r="A32" s="21" t="inlineStr">
+    <row r="34" ht="12.8" customHeight="1" s="14">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>quru</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>O quê?</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Que?</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>何？</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>What?</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13.8" customHeight="1" s="14">
-      <c r="A33" s="21" t="inlineStr">
+    <row r="35" ht="13.8" customHeight="1" s="14">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>kettle</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Consegue ouvir as palavras antigas que o vento sussurra? Eu vago pelo mundo para aprender a história do vento.</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Consegue ouvir as palavras antigas que o vento sussurra? Eu percorro este mundo para aprender a história do vento.</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>風の囁く古い言葉が、君には聞こえるかな？私は風の物語を学ぶために、この世界をさまよっているんだ。</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Can you hear the ancient words the wind whispers? I wander this world to learn the story of the wind.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="91" customHeight="1" s="14">
-      <c r="A34" s="21" t="inlineStr">
+    <row r="36" ht="91" customHeight="1" s="14">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>strange_girl</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Não gosto daqueles Pequenos. Falam coisas estranhas e é muito esquisito!_x000D_
-Não me coloque no mesmo saco que aqueles monstros._x000D_
-Quando o papai voltar, vou pedir pra nunca mais virmos aqui._x000D_
-Papai é um "cien-tista." Ele veio até este orfanato e então... aquela mulher monstro pediu algo pra ele, e ele disse que já voltava..._x000D_
-Papai vai voltar logo._x000D_
-Mesmo se me pedirem, não vou brincar com os Pequenos._x000D_
-Às vezes eles pegam e trazem coisas estranhas._x000D_
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Não gosto daqueles Pequeninos. Falam coisas esquisitas e é bem assustador!
+Não me coloque no balaio daqueles monstros.
+Quando o papai voltar, vou pedir para nunca mais virmos aqui.
+Papai é um "ci-en-tista." Ele veio a este berçário e depois... aquela mulher monstro pediu algo a ele, e ele disse que já voltava...
+O papai vai voltar logo.
+Mesmo que pedissem, não vou brincar com os Pequeninos.
+Às vezes, eles pegam e trazem coisas esquisitas.
 Aquela mulher monstro não é minha mamãe. Isso é óbvio!</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>リトルたちはきらいよ。あの子たち、おかしなことをしゃべって、ほんとに気持ちわるい！
 あのバケモノたちといっしょにしないでね。
@@ -4785,7 +5020,7 @@
 あのバケモノ女はママなんかじゃない。あたりまえでしょ？</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>I don't like those Littles. They talk weird things and it's really creepy!
 Don't lump me in with those monsters.
@@ -4798,47 +5033,47 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="12.8" customHeight="1" s="14">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="37" ht="12.8" customHeight="1" s="14">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>moyer</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Veio girar a roda dos prêmios, hein?</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Vem girar a roleta de prêmios, hein?</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>おっとガラガラを引きに来たのかい？</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Here to spin the prize wheel, huh?</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="105.95" customHeight="1" s="14">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="38" ht="105.95" customHeight="1" s="14">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>miko_mifu</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Somos ao mesmo tempo nossas bênçãos e maldições. Ao mudarmos nossa perspectiva, transformamos fraquezas em forças.
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Somos, ao mesmo tempo, nossas bênçãos e nossas maldições. Mudando a perspectiva, transformamos fraquezas em forças.
 Não há vida sem morte, nem céu sem inferno, nem encontro sem despedida, nem alegria sem tristeza.
-Como Donzela das Bênçãos, é meu dever conduzir os ritos de selamento todos os anos.
-As bênçãos de Lorde Kizuami podem ser recebidas por todos. É seu modo de interferir no mundo, e até os descrentes podem diverti-lo por um tempo.
-O arroz que cultivamos é abençoado com uma abundância de energia espiritual e é essencial para os ritos de selamento.
-Yufu era um deus perverso da negentropia que buscava trazer sua ilusão de paz a Ylva eliminando todos os conflitos entre os deuses.
-Quando assumi o posto de sacerdotisa, deixei meu antigo nome para trás e agora sou chamada de "Kinu". Um dia, uma de minhas filhas fará o mesmo.
-Não existe verão eterno; as estações passam e o inverno chega. As bênçãos não duram para sempre, mas a desgraça também não.</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
+Como Donzela das Bênçãos, é meu dever conduzir a vila nos ritos de selamento todo ano.
+As bênçãos do Lorde Kizuami podem ser recebidas por todos. É do jeito dele se intrometer no mundo, e até descrentes podem entretê-lo por um tempo.
+O arroz que cultivamos é abençoado com abundância de energia espiritual e é essencial aos ritos de selamento.
+Yufu era um deus da negaentropia maligno que buscava trazer sua ilusão de paz a Ylva eliminando toda discórdia entre os deuses.
+Quando ascendi a donzela do santuário, deixei de lado meu nome antigo e agora me chamo "Kinu". Um dia, uma das minhas filhas fará o mesmo.
+Não há verão eterno; as estações giram e o inverno chega. Bênçãos não duram para sempre, mas a desgraça também não.</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>私たちは祝福でもあり、呪いでもあります。見方を変えれば、弱さもまた強さに変わるのです。
 命に死がなく、天に地獄がなく、出会いに別れがなく、喜びに悲しみがない世界など、存在しないのです。
@@ -4850,7 +5085,7 @@
 永遠の夏はなく、季節は巡り、やがて冬が訪れます。祝福も永遠には続かず、不幸もまた同様です。</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>We are both our blessings and curses. By changing our perspectives, we turn our weaknesses into strengths.
 There is no life without death, no heaven without hell, no meeting without parting, no joy without sorrow.
@@ -4863,28 +5098,28 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="126.85" customHeight="1" s="14">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="39" ht="126.85" customHeight="1" s="14">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>miko_nefu</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Yufu era um deus perverso da negentropia que buscava manipular as guerras divinas e governar Ylva sem oposição.
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Yufu era um deus da negaentropia maligno que buscava manipular as guerras divinas e reinar sobre Ylva sem oposição.
 Realizamos danças cerimoniais na clareira diante da árvore sagrada.
-Lady Horome ama todos os mortais, e até os descrentes podem receber uma pequena bênção.
-Como Donzela das Lâminas, todos os anos eu realizo uma dança com espadas como parte dos ritos de selamento.
-As pétalas de cerejeira caem como as lágrimas da nossa deusa e tocam nossos corações com melancolia.
-Espadas cerimoniais têm um papel central nos rituais de adoração à nossa deusa.
-Lady Horome se encanta com crianças e abençoa aqueles que têm famílias numerosas. Nós, Nefu, nunca fomos um povo numeroso, e os que ganham seu favor assim são muito respeitados.
-Minha katana foi passada por gerações de donzelas do santuário.
-Cada Donzela das Lâminas busca acrescentar algo ao seu legado.
-Nossa deusa ensina que força e beleza não são opostas; as danças com espada dos Nefu procuram exemplificar ambas.
-A Vila Nefu foi fundada para proteger a árvore sagrada.</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
+A Dama Horome ama todos os mortais, e até descrentes podem receber uma pequena bênção.
+Como Donzela das Lâminas, todo ano executo uma dança das espadas como parte dos ritos de selamento.
+As flores de cerejeira caem como as lágrimas da nossa deusa e tocam nossos corações de melancolia.
+As espadas cerimoniais têm papel central nos ritos de culto da nossa deusa.
+A Dama Horome se deleita com crianças, e abençoa as que têm famílias grandes. Nós, Nefu, nunca fomos um povo numeroso, e quem conquista seu favor assim é muito respeitado.
+Minha katana passou por gerações de donzelas do santuário.
+Cada Donzela das Lâminas busca somar ao legado dela.
+Nossa deusa ensina que força e beleza não são opostos; as danças de espadas Nefu buscam exemplificar ambos.
+A Vila Nefu foi fundada para guardar a árvore sagrada.</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>ユフは、神々の戦争を操り、イルヴァを支配しようとした邪悪な負の神だった。
 私たちは神樹の広場で儀式の舞を捧げる。
@@ -4899,7 +5134,7 @@
 ネフの村は神樹を守るために築かれた。</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Yufu was a wicked negentropy god who sought to manipulate the divine wars and rule over Ylva unopposed.
 We hold ceremonial dances in the clearing before the sacred tree.
@@ -4915,29 +5150,29 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="126.85" customHeight="1" s="14">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="40" ht="126.85" customHeight="1" s="14">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>eureka</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Um viajante? Que ocasião rara.
-Fui encarregado de vigiar este local pelo meu deus. É uma grande honra, mas bem... pode ser entediante às vezes.
-Os ensinamentos de Lorde Yevan podem parecer drásticos, mas têm raízes em seu profundo amor e altas expectativas pelos mortais.
-Eu odeio máquinas. Elas não sangram.
-Interessado em um duelo? Eu preciso praticar um pouco.
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Uma viajante? Que ocasião rara.
+Recebi do meu deus a tarefa de vigiar este local. É uma grande honra, mas bem... às vezes fica entediante.
+Os ensinamentos do Lorde Yevan podem parecer drásticos, mas têm raiz no amor profundo dele e nas grandes expectativas pelos mortais.
+Odeio máquinas. Elas não sangram.
+Interessada num treino? Eu poderia usar um pouco de prática.
 Se ao menos o Billy não tivesse aqueles espinhos...
 Gatos... animais tão fofos.
-Ah, sinto falta do cheiro do campo de batalha. Alguma chance de você me levar a um?
-A paisagem aqui é linda, mas falta comida. Gosto de passar de vez em quando na Vila Mifu, ao norte daqui, pra conseguir mantimentos.
-Não vou te impedir se quiser desafiar o deus selado aqui. Lorde Yevan certamente se divertiria com isso.
-Éter é uma substância interessante. Com certeza vai mudar o rumo da humanidade — para o bem ou para o mal.
-Você acha que é rude acariciar aleatoriamente um povo-raposa fofinho?</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
+Ah, sinto falta do cheiro do campo de batalha. Por acaso você me levaria a um?
+A paisagem aqui é linda, mas a comida é escassa. Gosto de passar de vez em quando na Vila Mifu ao norte para pegar suprimentos.
+Não te impeço se quiser desafiar o deus selado aqui. Ao Lorde Yevan certamente agradaria.
+O éter é uma substância interessante. Vai mudar o caminho da humanidade, para o bem ou para o mal.
+Você acha grosseria fazer cafuné num foxfolk qualquer?</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>冒険者ですか？こんな場所まで来るとは、物好きですね。
 私は主にここの守護を任されています。大変な栄誉ではあるのですが...ときどき退屈ですね。
@@ -4953,7 +5188,7 @@
 初対面の狐族をモフモフするのって失礼でしょうか？</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>A traveler? What a rare occasion.
 I've been tasked to oversee this location by my god. It's a great honor, but well...can get boring at times.
@@ -4970,46 +5205,46 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="22.35" customHeight="1" s="14">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="41" ht="22.35" customHeight="1" s="14">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>merchant_inn_fox</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>O amuleto no meu pescoço? Claro que está cheio de arroz, não cultivamos trigo nesta vila.</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>この首飾り？もちろん中身は米よ。私たちの村では小麦は育てていないから。</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>The charm about my neck? Of course it's filled with rice, we don't grow wheat in this village.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="74.59999999999999" customHeight="1" s="14">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="42" ht="74.59999999999999" customHeight="1" s="14">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>merchant_inn_fox2</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Esta estalagem foi originalmente construída para receber peregrinos, mas a vila tem recebido muitos turistas ultimamente.
-Bem-vindo! Vai querer uma refeição, um banho ou talvez...?
-Não sei como a vila ficou tão popular de repente, mas fico mais do que feliz em estar tão ocupada!
-Os turistas continuam se aproximando demais da árvore sagrada, mesmo com os avisos da Misaki. Simplesmente não têm respeito!
-Conseguimos nos sustentar, mas eu não daria conta de todos esses turistas se a Vila Mifu não estivesse mandando comida do sul.
-Por que os humanos são tão fascinados pelas nossas orelhas e rabos?
-Misaki cuida do templo, enquanto eu administro a estalagem. Entre nós duas, não sobra muito pro ancião fazer!</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Esta estalagem foi construída originalmente para abrigar peregrinos, mas a vila recebe muitos turistas ultimamente.
+Bem-vindo! Quer uma refeição, um banho, ou talvez...?
+Não sei como a vila de repente ficou popular, mas estou mais que feliz em estar tão ocupada!
+Os turistas continuam chegando perto demais da árvore sagrada apesar dos avisos da Misaki. Eles simplesmente não têm respeito!
+Damos conta de nos sustentar, mas eu não daria conta de todos esses turistas se a Vila Mifu não nos mandasse comida do sul.
+Por que os humanos são tão fascinados por nossas orelhas e caudas?
+A Misaki cuida do templo, e eu comando a estalagem. Entre nós duas, não sobra muita coisa para o ancião fazer!</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>この宿は元々巡礼者を迎えるために建てられたのですが、最近は観光客も増えてきました。
 いらっしゃいませ！ お食事にしますか？ それともお風呂？ それとも…？
@@ -5020,7 +5255,7 @@
 ミサキは神殿を守り、私は宿を切り盛りしています。これじゃあ、長老がすることはあまり残っていませんね！</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>This inn was originally built to house pilgrims, but the village has had many tourists of late.
 Welcome! Would you like a meal, a bath, or perhaps...?
@@ -5032,27 +5267,27 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="105.95" customHeight="1" s="14">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="43" ht="105.95" customHeight="1" s="14">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>adv_kiria</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sabe por que eu fui criada? Não? Imaginei que não.
-Continuo sonhando com um lugar que parece ser meu lar, mas não consigo lembrar como chegar lá.
-Acordei com essa arma. Tão incômoda. Devo apunhalar ou atirar? Vou fazer os dois.
-"Oi! Aqui é a idol de todo mundo, Machine Doll Kiria-chan, kiri～" ... Eu tenho um módulo de idol? Quando é que gravei isso?
-Ouvi dizer que Mani das Máquinas sussurra para quem consegue ouvir o vazio. Talvez ele saiba por que eu fui criada.
-*zzt* Outra memória corrompida... o que eu estava fazendo aqui mesmo?
-*beep* Estamos realizando manutenção programada e voltaremos ao ar em breve.
-Algumas pessoas acham que sou um golemzinho? Bobagem.
-Bugs? Falhas? São recursos.
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Sabe por que fui feita? Não? Achei que não.
+Sigo sonhando com um lugar com cara de casa, mas não me lembro como chegar lá.
+Acordei com esta arma. Que incômodo. Apunhalo, ou atiro? Vou fazer os dois.
+"Hai! Sou a idol de todos, Boneca Máquina Kiria-chan, kiri～" ... Eu tenho um módulo de idol? Quando foi que gravei isto?
+Ouvi dizer que Mani da Máquina sussurra a quem pode ouvir o vazio. Talvez ele saiba por que fui feita.
+*zzt* Mais uma memória corrompida... o que eu estava fazendo aqui mesmo?
+*bip* Estamos realizando manutenção programada e voltaremos online em breve.
+Alguma gente acha que sou um golem miniatura? Absurdo.
+Bugs? Falhas? São funcionalidades.
 *encara* tch.</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>なぜ私が作られたのか知ってる？ いいえ？ だと思った。
  家みたいな場所を夢に見るけど、どうやってそこへ戻ればいいか思い出せない。
@@ -5066,7 +5301,7 @@
 *じっと見つめる* ちっ。</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Do you know why I was made? No? Didn’t think so.
 I keep dreaming of a place that looks like home, but I can't remember how to get there.
@@ -5081,27 +5316,27 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="105.95" customHeight="1" s="14">
-      <c r="A42" s="13" t="inlineStr">
+    <row r="44" ht="105.95" customHeight="1" s="14">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>adv_gaki</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Uma tulipa azul fantasma? Já viajei por muitos lugares, mas nunca vi uma.
-Tem uma doença estranha nova circulando... Será que vai me fazer crescer chifres~  
-Existe um deus que amaldiçoa as pessoas com feitiços esquisitos quando elas ficam bravas, então tome cuidado.
-Te digo, os dealers do cassino estão definitivamente trapaceando...!
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Uma tulipa azul fantasma? Já viajei para tudo quanto é lado, mas nunca vi uma.
+Tem uma doença estranha nova por aí... será que me faria crescer chifres~
+Há um deus que amaldiçoa as pessoas com feitiços esquisitos quando fica bravo, então cuidado.
+Estou te dizendo: os crupiês do cassino estão trapaceando, com certeza...!
 Ovo de um ovo♪ Fatia de uma fatia♪ Fatia de um ovo♪
-Sempre tem alguém melhor. E alguém pior que o pior. Qual deles é você, #brother2?
-Eu costumava ter outro chifre... não, outra espada, mas a perdi pelo caminho.
-Comer algo delicioso é pura felicidade♪
-A Princesa Fang chegou. Trate-a bem e rápido.
-Fofa e forte, é isso que faz de mim a Princesa Fang☆</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
+Sempre há alguém melhor. E alguém pior que o pior. Qual dos dois é você, #brother2?
+Eu tinha outro chifre... digo, outra espada, mas a perdi no caminho.
+Comer algo delicioso é pura bem-aventurança♪
+A Princesa Presa está aqui. Tratem-na bem, e rápido.
+Fofa e forte, é isso que me faz a Princesa Presa☆</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>空色のチューリップ？ 色々旅してきたけど見たことないよ。
 新しい奇妙な病気が流行ってるらしい……ツノでも生えないかな～。
@@ -5115,7 +5350,7 @@
 可愛くて強いのが牙姫ちゃんってワケ☆</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>A phantom azure tulip? I’ve traveled far and wide, but I’ve never seen one.
 There’s some new weird disease going around... I wonder if it’ll make me grow horns~
@@ -5130,27 +5365,27 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="105.95" customHeight="1" s="14">
-      <c r="A43" s="21" t="inlineStr">
+    <row r="45" ht="105.95" customHeight="1" s="14">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>adv_mesherada</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Eu me pergunto... estarão nossas almas entrelaçadas mais uma vez, aguardando o momento de cumprir nossa promessa?
-Se tu és aquele que procuro... certamente o destino nos sussurrará isso a ambos.
-Há algo em tua presença — uma paz que pensei perdida no tempo.
-Tua alma me soa familiar, como se nos encontrássemos muito antes dos nomes serem proferidos.
-Quem me dera que este momento pudesse durar, nem que fosse para sentir teu calor por mais um instante.
-És apenas um estranho gentil... ou o eco que tenho perseguido através do tempo?
-Estás diante de mim, e ainda assim não ouso nomear-te.
-Estranho... sinto-me mais segura quando estás por perto.
-Tu também sentes isso? Um fio esticado entre nós.
-Tantos caminhos... e ainda assim sempre te encontro no fim do meu.</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Será... que nossas almas estão mais uma vez entrelaçadas, aguardando o momento em que cumpriremos nossa promessa?
+Se tu és quem eu busco... com certeza o destino sussurrará a ambos.
+Há algo na tua presença: uma paz que eu pensava perdida no tempo.
+Tua alma parece familiar, como se nos encontrássemos muito antes de os nomes serem ditos.
+Quem dera este momento se estendesse, nem que fosse para sentir teu calor um pouco mais.
+És apenas uma estranha gentil... ou o eco que persegui através do tempo?
+Estás diante de mim, e ainda assim não ouso te nomear.
+Estranho... me sinto mais segura quando estás perto.
+Sentes isto também? Um fio esticado entre nós.
+Tantos caminhos... mas sempre te encontro no fim do meu.</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>魂が再び絡み合い、私たちが約束を果たすその時を待っている…そうではないか？ 
 もしそなたが私の探し人なら…きっと運命が二人に囁くだろう。
@@ -5164,7 +5399,7 @@
 いくつもの道を歩んでも…その先には必ずそなたがいるのだ。</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>I wonder... are our souls once more intertwined, waiting for the moment when we shall fulfill our promise?
 If thou art the one I seek... surely fate shall whisper it to us both.
@@ -5179,27 +5414,27 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="105.95" customHeight="1" s="14">
-      <c r="A44" s="21" t="inlineStr">
+    <row r="46" ht="105.95" customHeight="1" s="14">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>olderyoungersister</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Eu me pergunto quando nasci, #brother2? Foi há muito, muito tempo, #brother2...
-Eu andei por este mundo todo esse tempo, procurando por você, #brother2... e então te encontrei!
-Vamos ficar juntos para sempre, né, #brother2...? Só fiquei um pouco assustado, só isso, #brother2.
-Quero poder fazer tudo por você, #brother2 – lutar, cuidar da casa, tudo.
-Deus pode ser tão cruel às vezes, #brother2...
-Eu nunca vou te prender, #brother2! Eu prometo!
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>Será quando nasci, #brother2? Foi há muito, muito tempo, #brother2...
+Andei vagando por este mundo todo esse tempo, procurando por você, #brother2... e então te encontrei!
+Ficaremos juntos para sempre, né, #brother2...? É que fiquei com um medinho, só isso, #brother2.
+Quero poder fazer tudo por você, #brother2: lutar, trabalhos de casa, tudo.
+Deus às vezes pode ser tão cruel, #brother2...
+Nunca vou te prender, #brother2! Prometo!
 Parece que há um poder do caos na minha canção.
-Ouvi dizer que existem outras irmãs neste mundo que não são de sangue, #brother2!
-Quero me enroscar com a snow putit-chan! Quero muito, #brother2!
-Existem snow putit-chans de cores diferentes, #brother2. Seria tão bom se pudéssemos acolher todas elas, #brother2.</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
+Ouvi dizer que há outras irmãs neste mundo que não são suas irmãs de sangue, #brother2!
+Quero fazer cafuné no snow putit-chan! Quero mesmo, #brother2!
+Há snow putit-chans de cores diferentes, #brother2. Seria tão bom se pudéssemos acolher todos, #brother2.</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>私がいつ生まれたのか気になるの#brother2？遠い遠い遥か昔の事だよ#brother2…
 ずっと#brother2を求めてこの世界を彷徨っていたの…そしたらいたのよ#brother2が！
@@ -5213,7 +5448,7 @@
 雪プチちゃんには色の違う子たちがいるんだよ#brother2。みんなお迎えできると嬉しいね#brother2。</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>I wonder when I was born, #brother2? It was a long, long time ago, #brother2...
 I’ve been wandering this world all this time, searching for you, #brother2... and then I found you!
@@ -5228,26 +5463,26 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="95.5" customHeight="1" s="14">
-      <c r="A45" s="21" t="inlineStr">
+    <row r="47" ht="95.5" customHeight="1" s="14">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>fairy_nanasu</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Eu sou Nanas, a fada berinjela!
-Qual é minha comida favorita? Berinjela, é claro!
-Specwing é um lugar muito agradável, todo mundo está dançando feliz.
-A parte mais gratificante de uma aventura é o vínculo que se cria por aventurar-se juntos!
-Bebi muito com novos amigos que conheci durante minhas aventuras, foi muito divertido.
-Claro, houve momentos tristes, mas eu segui em frente acreditando que encontraria novas pessoas, e é por isso que estou aqui hoje.
-Os encontros chegarão ao fim em algum momento, mas acredito que o que ganhei com eles não será em vão.
-A fada berinjela azul que dizem ter criado Specwing, eu gostaria de superá-la algum dia.
-Quando eu ainda era muito jovem, treinei lutas com uma fada berinjela azul. Ela era uma fada, mas muito resistente.</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Sou a Nanasu, a fada da berinjela!
+Minha comida favorita? Berinjela, claro!
+Specwing é um lugar muito legal, todo mundo dança feliz.
+A parte mais gratificante de uma aventura é o vínculo que você ganha aventurando junto!
+Bebi bastante com amigos novos que fiz nas minhas aventuras, foi muito divertido.
+Claro, houve momentos tristes, mas segui em frente acreditando que conheceria gente nova, e é por isso que estou aqui hoje.
+Os encontros acabam em algum momento, mas acredito que o que ganhei deles não será em vão.
+A fada da berinjela azul que dizem ter criado Specwing: gostaria de superá-la um dia.
+quando eu era bem novinha, treinei luta com uma fada da berinjela azul. Ela era fada, mas bem resistente.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>ボクはナナス、ナスの妖精だよ～。
 好きな物はなにかって？もちろんナスだよ～。
@@ -5260,7 +5495,7 @@
 実は幼いころに青いナスの妖精に稽古をつけてもらったことがあるんだよぉ。彼女は妖精だったけど、とっても頑丈だったよぉ～。</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>I am Nanasu, the eggplant fairy!
 What's my favorite food? Eggplant, of course!
@@ -5274,27 +5509,27 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="116.4" customHeight="1" s="14">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="48" ht="116.4" customHeight="1" s="14">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>fairy_raina</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sou Raina! Me toque descuidadamente e vou fazer você formigar!
-Oh, aventureiro. Você precisa de algo comigo?
-Meu relacionamento com Poina? Bem~ tipo parceiras de travessuras, eu acho? Mas estamos em aventuras juntas há muito tempo, de um jeito ou de outro.
-Eu não desgosto de Nanasu, sabe? Eu só... quero pregar uma travessurinha e transformá-la em berinjela grelhada!
-Na primeira vez que Poina, Nanasu e eu fomos em aventura juntas, Nanasu errou feio e quase morreu... Consegui salvar a situação com meu raciocínio rápido, mas sério...
-Durante a disputa das bolsas, eu estava em uma missão separada de Nanasu, mas eu vou em aventuras com ela às vezes. Bem, na maioria das vezes ela é só a isca!
-Ultimamente, as fadas de Specwing têm ido em mais aventuras. Bem, ter mais rivais não é tão ruim assim!
-Quando eu tive febre, Nanasu cuidou de mim. Não consegui agradecer a ela na hora, mas sou grata.
-A Fada da Berinjela Azul, que dizem ser a fundadora de Specwing...? Ah, ela... Eu costumava treinar com ela também, mas nunca venci uma única luta!
-Eu estava planejando me vingar da Fada da Berinjela Azul algum dia, mas antes que percebesse, ela tinha desaparecido! ...Parece que ela escapou impune, e isso é tão frustrante!</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Sou a Raina! Me toque sem cuidado e te deixarei formigando!
+Oh, aventureiro. Precisa de algo comigo?
+Minha relação com a Poina? Bem~ parceiras de travessura, digamos? Mas aventuramos juntas há eras, de um jeito ou de outro.
+Eu não desgosto da Nanasu, sabia? Eu só... quero pregar uma peça e transformá-la em berinjela grelhada!
+Na primeira vez que a Poina, a Nanasu e eu fomos aventurar juntas, a Nanasu vacilou e quase morreu... salvei o dia com meu raciocínio rápido, mas sério...
+Na disputa da bolsa, eu estava numa missão separada da Nanasu, mas aventuro com ela às vezes. Bom, na maioria das vezes ela é só a isca!
+Ultimamente, as fadas de Specwing estão aventurando mais. Bom, ter mais rivais também não é ruim!
+Quando tive febre, a Nanasu cuidou de mim. Não consegui agradecer na época, mas sou grata.
+A Fada da Berinjela Azul, dizem que fundou Specwing...? Ah, ela... eu também treinava com ela, mas nunca ganhei uma luta sequer!
+Eu planejava me vingar da Fada da Berinjela Azul um dia, mas quando vi, ela tinha sumido! ...Parece que ela se safou, e é tão frustrante!</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>アタシはライナ！迂闊に触れると痺れさせちゃうよっ！
 あら、冒険者さん。アタシに何か用？
@@ -5308,7 +5543,7 @@
 青いナスの妖精にはいつかリベンジしようと思ってた、でもいつの間にかどっかに行っちゃった！…勝ち逃げされた気分でくやしい！</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>I'm Raina! Touch me carelessly and I'll make you tingle!
 Oh, adventurer. You need something from me?
@@ -5323,27 +5558,27 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="105.95" customHeight="1" s="14">
-      <c r="A47" s="21" t="inlineStr">
+    <row r="49" ht="105.95" customHeight="1" s="14">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>fairy_poina</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sou Poina. Diga uma coisa errada e vou atacar você com veneno.
-O quê? Você precisa de algo?
-Raina às vezes subestima a luta. Quantas vezes tenho que dizer que aventura não é brincadeira, idiota...
-Nanasu é doce demais. Ela diz que valoriza laços, mas se isso é tudo que ela tem, vai tropeçar algum dia...
-Conheço Raina há muito tempo, mas só penso nela como uma colega travessa. Ainda assim, não me importo de ir em aventuras com ela.
-Prefiro lançar ataques surpresa, mas Raina sempre avança de cabeça, levando a um desgaste desnecessário... Que idiota...
-Você ouviu sobre a primeira aventura de Raina com Nanasu? Naquela época, Nanasu estava chorando porque achava que tinha colocado todos em perigo.
-Nanasu uma vez procurou desesperadamente por algo que perdi. Mesmo eu sendo sempre a que prega peças... idiota...
-Muito tempo atrás, treinei com Nanasu e Raina sob a fada da berinjela azul. Mas meus ataques de veneno mal a afetavam.
-Raina, Nanasu e eu podemos derrotar a fada da berinjela azul? Mas ela está viajando por aí há muito tempo...</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>Sou a Poina. Diga uma coisa errada e te ataco com veneno.
+Que? Precisa de algo?
+A Raina às vezes subestima a luta. Quantas vezes tenho de te dizer que aventura não é jogo, idiota...
+A Nanasu é doce demais. Diz que valoriza vínculos, mas se for só isso que ela tem, vai tropeçar um dia...
+Conheço a Raina há muito tempo, mas só a vejo como parceira de peças. Ainda assim, não me importo de aventurar com ela.
+Prefiro lançar ataques surpresa, mas a Raina sempre avança de cabeça, gerando desgaste desnecessário... Que idiota...
+Soube da primeira aventura da Raina com a Nanasu? Naquela época, a Nanasu chorava porque achava que tinha posto todos em perigo.
+A Nanasu certa vez procurou desesperadamente algo que eu perdi. E olha que sempre sou eu que faço as peças... idiota...
+Há muito tempo, treinei com a Nanasu e a Raina sob a fada da berinjela azul. Mas meus ataques de veneno quase não a afetaram.
+A Raina, a Nanasu e eu conseguimos derrotar a fada da berinjela azul? Mas ela viaja por algum lugar há muito tempo...</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>私はポイナ、余計な事言うと毒を喰らわせるからな。
 …なんだ？何か用か？
@@ -5357,7 +5592,7 @@
 今の私とライナ、そしてナナスの3人であれば青いナスの妖精に勝てるだろうか？だがアイツはもう何処かに行って久しいからな…</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>I'm Poina. Say one wrong thing and I'll attack you with poison.
 What? You need something?
@@ -5372,27 +5607,27 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="105.95" customHeight="1" s="14">
-      <c r="A48" s="21" t="inlineStr">
+    <row r="50" ht="105.95" customHeight="1" s="14">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>girl_blue</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Snow Putit é simplesmente fofo demais... hehe.
-Eu queria ser tão livre quanto um gato... Se existe um deus dos gatos, ele deve ser a própria liberdade.
-Tudo que quero é uma vida normal... Então por que problemas sempre me encontram? *suspiro*
-Aquele aventureiro fala tão estranhamente... e ainda assim, de alguma forma conseguimos conversar.
-Aquele aventureiro fofo, parecido com uma boneca... sempre procurando por alguém.
-Aquele aventureiro com asas negras... eles parecem muito legais.
-Aquele aventureiro mago... carregando um livro que parece meio perigoso.
-Aquele aventureiro que acredita no destino... tão apaixonado, hein.
-Um aventureiro que... 'inala gatos'? ...Espera, o quê?
-Aquela padaria da bruxa em Mysilia é tão adorável... Uma loja de verdade, bem no meio da cidade. Uma bruxa... e uma padeira!</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>O Snow Putit é simplesmente fofo demais... hehe.
+Queria ser livre como um gato... Se existe um deus-gato, deve ser a liberdade em pessoa.
+Só quero uma vida normal... Então por que a encrenca sempre me acha? *suspiro*
+Aquele aventureiro fala tão estranho... e mesmo assim, de algum jeito, acabamos conversando.
+Aquela aventureira fofa, de boneca... sempre procurando por alguém.
+Aquele aventureiro de asas negras... tem um estilo muito legal.
+Aquela aventureira maga... carregando um livro com cara de perigoso.
+Aquele aventureiro que acredita no destino... que apaixonado, hein.
+Um aventureiro que... 'inha gatos'? ...Espera, como?
+A padaria daquela bruxa em Mysilia é tão linda... Uma loja de verdade, no meio da cidade. Uma bruxa... e uma padeira!</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>雪プチちゃん、かわいいですよね……フフフ……。
 ねこの自由さには憧れます。ねこの神様がいたらきっと自由そのものなんだろうなあ。
@@ -5406,7 +5641,7 @@
 ミシリアにある魔女のパン屋さん、素敵ですよね！魔女で、パン屋さん！</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Snow Putit is just too cute... hehe.
 I wish I were as free as a cat... If there’s a cat god, they must be freedom itself.
@@ -5421,26 +5656,26 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="95.5" customHeight="1" s="14">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="51" ht="95.5" customHeight="1" s="14">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>rodwyn</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Eu só uso ingredientes da mais alta qualidade para meus assados.
-Gostaria de ver minha coleção de vassouras?
-Vejamos... Língua de tritão. Olho de abelha. Oh? Desculpe, não percebi você aí. Estava pensando em uma nova receita.
-Você viu algum gato por perto?
-Claro que você pode assar pão em um forno! Você não faz?
-Minha estante de química? Essas são obviamente especiarias!
-Meu chapéu? Legal, né?
-(Você a observa despejar o que parece ser um saco de insetos em uma tigela de mistura.)
-Você com certeza faz muitas perguntas...</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Só uso ingredientes da mais alta qualidade nos meus assados.
+Quer conhecer minha coleção de vassouras?
+Vejamos… Língua de girino. Olho de abelha. Oh? Desculpa, nem te vi aí. Estava pensando numa receita nova.
+Viu algum gato por perto?
+Claro que se faz pão num forno de oleiro! Você não faz?
+Minha estante de química? São obviamente temperos!
+Meu chapéu? Estiloso, né?
+(Você a vê despejar o que parece ser um saco de insetos numa tigela de mistura.)
+Você faz mesmo um montão de perguntas…</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>私の料理に使われているのは全部最高級の素材。
 私のホウキコレクション、見てみたい？
@@ -5453,7 +5688,7 @@
 ……質問が多いのねぇ…</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>I only use the highest quality ingredients for my baked goods.
 Would you like to see my broom collection?
@@ -5526,27 +5761,27 @@
           <t>eyth</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>…bneep…
+…zzzzzz…
+…zshh…bip……</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>…ピー…
+…ザザザ…
+…ザザ…ガガ…</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>…bneep…
 …zzzzzz…
 …zshh…beep……</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>…ピー…
-…ザザザ…
-…ザザ…ガガ…</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>…bneep…
-…zzzzzz…
-…zshh…beep……</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="168.65" customHeight="1" s="14">
       <c r="A6" s="13" t="inlineStr">
@@ -5554,22 +5789,22 @@
           <t>jure</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>…c-cafuné…cafuné…
-…abraaaço…
-…abraaaaaaço…
-…pronto…pronto…
-…v-você é um idiota…
-…n-não se confunda, ok…
-…n-não é como se eu estivesse fazendo isso por você ou algo assim…
-…n-não é…de verdade…
-…eu só…a-aconteceu de eu ter um tempo, só isso…
-…mm…pronto…
-…v-você deveria…se deixar relaxar…
-…f-fuuaaah…
-…eh-ho…eh-ho…
-…oh…você que vaga…
+…a-abraço…
+…a-braaço…
+…pronto…assim…
+…s-seu idiota…
+…n-não entenda errado, tá…
+…n-não é como se eu estivesse fazendo isso por você ou qualquer coisa…
+…n-não é…de verdade não…
+…eu só…a-aconteceu de ter um tempinho, só isso…
+…hm…aqui…
+…v-você devia…se permitir relaxar…
+…f-fuaaah…
+…eh-hô…eh-hô…
+…oh…você que vagueia…
 …c-cura…
 …para suas…almas feridas…</t>
         </is>
@@ -5621,20 +5856,20 @@
           <t>opatos</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>…grrr…tritura tritura…
-…goooogoooo……
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>…grrr…raspa raspa…
+…grooogooot……
 …estrondo……
-…crashhh……
+…CRACCC……
 …shrrk…shraaa……
-…raspa…raaaaaspa……
+…raspa…raspaaa……
 …gooo……grooo……
-…rangido…craaack……
-…crack…crack crack……
-…grão…tritura tritura……
-…bum……bum……
-…boom……booom……
+…creeak…craacck……
+…crac…crac crac……
+…grão…raspa raspa……
+…TUM……TUM……
+…bum……buuum……
 …dunn……
 …muwahaha…
 …mwahahahaha…
@@ -5703,30 +5938,30 @@
           <t>horome</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>…está tudo bem…mamãe está bem aqui com você…
-…boa noite…docinho…
-…você pode descansar em mamãe…está tudo bem…
-…só estar aqui…já é o suficiente…
-…aqui…cafunés gentis…você está seguro…
-…isso mesmo…relaxe…
-…pronto pronto…
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>…tá tudo bem…a mamãe está aqui com você…
+…boa noite…meu bem…
+…pode encostar na mamãe…tá tudo bem…
+…só estar aqui…já basta…
+…aqui…cafuné suave…você está seguro…
+…isso…relaxa…
+…prontinho…
 …vamos ficar quentinhos…assim mesmo…
-…cafuné…cafuné…deixe ir…
-…mm…pronto pronto…bom menino…
-…quentinho…aconchegante…assim mesmo…
-…não pense mais…agora…
-…fofinho, não é…te acalma…
-…vou te envolver…com minha cauda…
-…fofo…mofu…aqui…minha cauda…
-…esfrega…esfrega…gentilmente…envolvendo você…
-…quentinho…aconchegante…ficando com sono…
-…fique perto…assim…
+…caf…caf…deixa ir…
+…hm…prontinho…bom menino…
+…quente…aconchegante…assim mesmo…
+…chega de pensar…agora…
+…fofinho, né…isso acalma…
+…vou enrolar você…com minha cauda…
+…fuff…mofu…aqui…minha cauda…
+…coça…coça…de leve…te enrolando…
+…quente…aconchegante…dando sono…
+…fica pertinho…assim…
 …inspira…expira…comigo…
 …é a mamãe…
-…cafuné…cafuné…deixe ir…
-…pronto…abraaaaaaaço…</t>
+…caf…caf…deixa ir…
+…pronto…a-braaaaaaaaaço…</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -5788,7 +6023,7 @@
           <t>demitas</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">…heh heh heh……
 …heh heh……
@@ -5801,7 +6036,7 @@
 …heh… heh… heh……
 …heh… heh…
 …heh heh… heh…
-…rápido…
+…apresse-se…
 …heh heh heh heh…
 …heh heh heh heh heh…
 …heh heh… heh heh… heh heh…
@@ -5867,38 +6102,38 @@
           <t>lulwy</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>…oh… então é disso que você gosta…?
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>…ah… então é disso que você gosta…?
 …que degenerado…
 …você… porco imundo… ahaha…!
-…oh… você está tremendo… que adorável…
-…você gosta de ser desprezado… não é…?
+…ah… você está tremendo… que adorável…
+…você gosta de ser humilhado… não gosta…?
 …um mero inseto… ahahaha…
-…tão pequeno… realmente… minúsculo…
+…tão pequeno… de verdade… minúsculo…
 …aha… divertido…
-…ahaha… picado… tão picado…!
+…ahaha… moído… tão moído…!
 …patético…
-…vamos… me mostre mais…
-…fazendo essa cara… na frente de uma deusa…
+…anda… me mostra mais…
+…fazendo essa cara… diante de uma deusa…
 …ahaha… porco patético…
 …essa cara… absolutamente… vergonhosa…
-…vamos… rasteje no chão…
+…anda… rasteja no chão…
 …aha… o vento está rindo…
-…você acha… que poderia olhar para uma deusa…?
-…levante a cabeça de novo… e você será picado…
+…acha… que pode olhar para uma deusa…?
+…erga a cabeça de novo… e você vira moído…
 …ahah… mortal miserável…
-…você é… tão fácil de ler…
-…ahaha… você é impossível…
-…patético… sendo insultado… e gostando disso…
+…você… é fácil demais de ler…
+…ahaha… você não tem jeito…
+…patético… ser insultado… e gostar…
 …você… pervertido…
-…ah… aquilo agora… foi bom, não foi…?
+…ah… esse agora… foi gostoso, não foi…?
 …lixo…
-…continue… inútil…
+…continue… sem valor…
 …ei… você tem segundas intenções…?
-…ah… acertei em cheio…!
-…sua mera existência… é irritante…aha…
-…realmente… impossível…pervertido…</t>
+…ah… na mosca…!
+…a sua mera existência… é irritante… aha…
+…verdade… sem jeito… pervertido…</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5976,17 +6211,17 @@
           <t>ehekatl</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> @3UMIMYAA!
- @3Caranguejo rei!
-…esfrega…
-…esfrega esfrega…
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@3UMIMYAA!
+@3Caranguejo real!
+…coça…
+…coça coça…
 …lambe…
 …lambe lambe…
-…bonk…
+…tum…
 …meo…
-…meo… w…
+…meo… m…
 …m… </t>
         </is>
       </c>
@@ -6025,26 +6260,26 @@
           <t>fox_maid</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>…Bom dia, Mestre…
 …Permita-me servir seu chá…
-…Cuidei de seus assuntos enquanto estava fora…
-…Eu não quero ser a única sem peito na minha família…
-…Você viu a escada…?
-…Você tem algo no seu rosto…
-…Farei com prazer para que você não precise fazer…
-…Quanto mais mochi eu tenho que socar…?
+…Cuidei dos seus assuntos enquanto estava fora…
+…Não quero ser a única achatada da minha família…
+…Viu o escadinha por aí…?
+…Tem algo no seu rosto…
+…Farei com prazer para você não precisar…
+…Quanto mais mochi eu tenho de socar…?
 …Kyaaa!…
 …M-mestre…!
-…É meu dever cuidar de você…mas mesmo que não fosse, eu faria de qualquer jeito…
+…É meu dever cuidar de você…mas mesmo que não fosse, faria de qualquer jeito…
 …O que gostaria de jantar hoje, Mestre…?
-…Abre a boca~♥
-…Ouvi dizer que tartaruga de casca mole é boa para vigor…
-…Você não precisa me levantar para eu alcançar a prateleira alta…
-…É estranho estar tão perto de você quando sou sua empregada…
-…Certifique-se de fazer exercícios, ok…?
-…Eu fiz um bom trabalho, Mestre…?
+…Abra bem a boquinha~♥
+…Ouvi dizer que tartaruga é boa para o vigor…
+…Não precisa me erguer para eu alcançar a prateleira de cima…
+…É esquisito estar tão pertinho de você sendo eu sua empregada…
+…Não deixe de se exercitar, tá…?
+…Fiz um bom trabalho, Mestre…?
 …Leite? M-mas…</t>
         </is>
       </c>
